--- a/example-0001_dra_metadata.xlsx
+++ b/example-0001_dra_metadata.xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="23232" windowHeight="10512" tabRatio="430"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="23040" windowHeight="10536" tabRatio="430"/>
   </bookViews>
   <sheets>
     <sheet name="Readme" sheetId="9" r:id="rId1"/>
@@ -236,7 +236,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="263" uniqueCount="216">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="263" uniqueCount="217">
   <si>
     <t>Library Source</t>
   </si>
@@ -305,18 +305,6 @@
   </si>
   <si>
     <t>Experiment Referenced</t>
-  </si>
-  <si>
-    <t>d3f8993745235bf50c0b0960587372a3</t>
-  </si>
-  <si>
-    <t>952a547197955ba7ec1e7fe0fca78fbd</t>
-  </si>
-  <si>
-    <t>1983835b5b2701796a3c9b73f7885f5a</t>
-  </si>
-  <si>
-    <t>9d411f31be0486e26da61c038712131e</t>
   </si>
   <si>
     <t>WGS</t>
@@ -804,22 +792,13 @@
     <t>Example experiment title 1</t>
   </si>
   <si>
-    <t>SAMD00061135</t>
-  </si>
-  <si>
     <t>Example library name 1</t>
   </si>
   <si>
     <t>Example library construction protocol 1</t>
   </si>
   <si>
-    <t>95</t>
-  </si>
-  <si>
     <t>Example experiment title 2</t>
-  </si>
-  <si>
-    <t>SAMD00061136</t>
   </si>
   <si>
     <t>Example library name 2</t>
@@ -829,9 +808,6 @@
   </si>
   <si>
     <t>Example experiment title 3</t>
-  </si>
-  <si>
-    <t>SAMD00061137</t>
   </si>
   <si>
     <t>Example library name 3</t>
@@ -847,9 +823,6 @@
   </si>
   <si>
     <t>Example experiment title 4</t>
-  </si>
-  <si>
-    <t>SAMD00061138</t>
   </si>
   <si>
     <t>Example library name 4</t>
@@ -891,13 +864,48 @@
     <t>accession.tab</t>
   </si>
   <si>
-    <t>e3b53db5cdcaad21748ad0d1a724e3f7</t>
-  </si>
-  <si>
     <t>run4.bam</t>
   </si>
   <si>
-    <t>c070fed15017c10962b905aac452c44e</t>
+    <t>101</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>202</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>SAMD00218641</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>SAMD00218642</t>
+  </si>
+  <si>
+    <t>SAMD00218643</t>
+  </si>
+  <si>
+    <t>SAMD00218644</t>
+  </si>
+  <si>
+    <t>537e142c7714d654276ac1e79b42a7b0</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>c5779305e16004ff03afe52a0efffaf4</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>3f9d4730efc67d64ad331e9bfb8f6369</t>
+  </si>
+  <si>
+    <t>e3fc484ca37e30ecbb855bb0577a4026</t>
+  </si>
+  <si>
+    <t>c9f343549f617c61c5219c77f135195f</t>
+  </si>
+  <si>
+    <t>9c349d8e07027cd6cfc49219a321a9af</t>
   </si>
 </sst>
 </file>
@@ -1375,27 +1383,27 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="5" t="s">
-        <v>174</v>
+        <v>170</v>
       </c>
     </row>
     <row r="2" spans="1:1">
       <c r="A2" s="5" t="s">
-        <v>113</v>
+        <v>109</v>
       </c>
     </row>
     <row r="4" spans="1:1" ht="26.4">
       <c r="A4" s="7" t="s">
-        <v>175</v>
+        <v>171</v>
       </c>
     </row>
     <row r="6" spans="1:1">
       <c r="A6" s="16" t="s">
-        <v>172</v>
+        <v>168</v>
       </c>
     </row>
     <row r="7" spans="1:1">
       <c r="A7" s="18" t="s">
-        <v>173</v>
+        <v>169</v>
       </c>
     </row>
   </sheetData>
@@ -1421,21 +1429,21 @@
   <sheetData>
     <row r="1" spans="1:3">
       <c r="A1" s="16" t="s">
-        <v>138</v>
+        <v>134</v>
       </c>
       <c r="B1" s="16" t="s">
-        <v>137</v>
+        <v>133</v>
       </c>
       <c r="C1" s="17" t="s">
-        <v>139</v>
+        <v>135</v>
       </c>
     </row>
     <row r="2" spans="1:3">
       <c r="A2" s="5" t="s">
-        <v>176</v>
+        <v>172</v>
       </c>
       <c r="B2" s="5" t="s">
-        <v>177</v>
+        <v>173</v>
       </c>
       <c r="C2" s="3">
         <v>45292</v>
@@ -1443,26 +1451,26 @@
     </row>
     <row r="4" spans="1:3">
       <c r="A4" s="16" t="s">
-        <v>140</v>
+        <v>136</v>
       </c>
       <c r="B4" s="16" t="s">
-        <v>141</v>
+        <v>137</v>
       </c>
     </row>
     <row r="5" spans="1:3">
       <c r="A5" s="5" t="s">
-        <v>178</v>
+        <v>174</v>
       </c>
       <c r="B5" s="6" t="s">
-        <v>179</v>
+        <v>175</v>
       </c>
     </row>
     <row r="6" spans="1:3">
       <c r="A6" s="5" t="s">
-        <v>180</v>
+        <v>176</v>
       </c>
       <c r="B6" t="s">
-        <v>181</v>
+        <v>177</v>
       </c>
     </row>
     <row r="7" spans="1:3">
@@ -1498,7 +1506,7 @@
   <sheetData>
     <row r="1" spans="1:13">
       <c r="A1" s="16" t="s">
-        <v>149</v>
+        <v>145</v>
       </c>
       <c r="B1" s="16" t="s">
         <v>9</v>
@@ -1539,16 +1547,16 @@
     </row>
     <row r="2" spans="1:13">
       <c r="A2" s="9" t="s">
-        <v>182</v>
+        <v>178</v>
       </c>
       <c r="B2" s="9" t="s">
-        <v>183</v>
+        <v>179</v>
       </c>
       <c r="C2" s="9" t="s">
-        <v>184</v>
+        <v>207</v>
       </c>
       <c r="D2" s="9" t="s">
-        <v>185</v>
+        <v>180</v>
       </c>
       <c r="E2" s="9" t="s">
         <v>3</v>
@@ -1557,33 +1565,33 @@
         <v>18</v>
       </c>
       <c r="G2" s="9" t="s">
-        <v>27</v>
+        <v>23</v>
       </c>
       <c r="H2" s="9" t="s">
-        <v>186</v>
+        <v>181</v>
       </c>
       <c r="I2" s="9" t="s">
-        <v>70</v>
+        <v>66</v>
       </c>
       <c r="J2" s="9" t="s">
         <v>20</v>
       </c>
       <c r="M2" s="9" t="s">
-        <v>187</v>
+        <v>205</v>
       </c>
     </row>
     <row r="3" spans="1:13">
       <c r="A3" s="9" t="s">
-        <v>143</v>
+        <v>139</v>
       </c>
       <c r="B3" s="9" t="s">
-        <v>188</v>
+        <v>182</v>
       </c>
       <c r="C3" s="9" t="s">
-        <v>189</v>
+        <v>208</v>
       </c>
       <c r="D3" s="9" t="s">
-        <v>190</v>
+        <v>183</v>
       </c>
       <c r="E3" s="9" t="s">
         <v>3</v>
@@ -1592,33 +1600,33 @@
         <v>18</v>
       </c>
       <c r="G3" s="9" t="s">
-        <v>27</v>
+        <v>23</v>
       </c>
       <c r="H3" s="9" t="s">
-        <v>191</v>
+        <v>184</v>
       </c>
       <c r="I3" s="9" t="s">
-        <v>70</v>
+        <v>66</v>
       </c>
       <c r="J3" s="9" t="s">
         <v>20</v>
       </c>
       <c r="M3" s="9" t="s">
-        <v>187</v>
+        <v>205</v>
       </c>
     </row>
     <row r="4" spans="1:13">
       <c r="A4" s="9" t="s">
-        <v>144</v>
+        <v>140</v>
       </c>
       <c r="B4" s="9" t="s">
-        <v>192</v>
+        <v>185</v>
       </c>
       <c r="C4" s="9" t="s">
-        <v>193</v>
+        <v>209</v>
       </c>
       <c r="D4" s="9" t="s">
-        <v>194</v>
+        <v>186</v>
       </c>
       <c r="E4" s="9" t="s">
         <v>3</v>
@@ -1627,36 +1635,36 @@
         <v>18</v>
       </c>
       <c r="G4" s="9" t="s">
-        <v>27</v>
+        <v>23</v>
       </c>
       <c r="H4" s="9" t="s">
-        <v>195</v>
+        <v>187</v>
       </c>
       <c r="I4" s="9" t="s">
-        <v>64</v>
+        <v>60</v>
       </c>
       <c r="J4" s="9" t="s">
         <v>21</v>
       </c>
       <c r="K4" s="9" t="s">
-        <v>196</v>
+        <v>188</v>
       </c>
       <c r="M4" s="9" t="s">
-        <v>197</v>
+        <v>189</v>
       </c>
     </row>
     <row r="5" spans="1:13">
       <c r="A5" s="9" t="s">
-        <v>145</v>
+        <v>141</v>
       </c>
       <c r="B5" s="9" t="s">
-        <v>198</v>
+        <v>190</v>
       </c>
       <c r="C5" s="9" t="s">
-        <v>199</v>
+        <v>210</v>
       </c>
       <c r="D5" s="9" t="s">
-        <v>200</v>
+        <v>191</v>
       </c>
       <c r="E5" s="9" t="s">
         <v>3</v>
@@ -1665,22 +1673,22 @@
         <v>18</v>
       </c>
       <c r="G5" s="9" t="s">
-        <v>27</v>
+        <v>23</v>
       </c>
       <c r="H5" s="9" t="s">
-        <v>201</v>
+        <v>192</v>
       </c>
       <c r="I5" s="9" t="s">
-        <v>64</v>
+        <v>60</v>
       </c>
       <c r="J5" s="9" t="s">
         <v>21</v>
       </c>
       <c r="K5" s="9" t="s">
-        <v>202</v>
+        <v>193</v>
       </c>
       <c r="M5" s="9" t="s">
-        <v>197</v>
+        <v>206</v>
       </c>
     </row>
   </sheetData>
@@ -1740,7 +1748,7 @@
   <sheetData>
     <row r="1" spans="1:3">
       <c r="A1" s="16" t="s">
-        <v>150</v>
+        <v>146</v>
       </c>
       <c r="B1" s="16" t="s">
         <v>9</v>
@@ -1751,46 +1759,46 @@
     </row>
     <row r="2" spans="1:3">
       <c r="A2" s="9" t="s">
-        <v>203</v>
+        <v>194</v>
       </c>
       <c r="B2" s="9" t="s">
-        <v>204</v>
+        <v>195</v>
       </c>
       <c r="C2" s="9" t="s">
-        <v>182</v>
+        <v>178</v>
       </c>
     </row>
     <row r="3" spans="1:3">
       <c r="A3" s="9" t="s">
-        <v>146</v>
+        <v>142</v>
       </c>
       <c r="B3" s="9" t="s">
-        <v>205</v>
+        <v>196</v>
       </c>
       <c r="C3" s="9" t="s">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3">
+      <c r="A4" s="9" t="s">
         <v>143</v>
       </c>
-    </row>
-    <row r="4" spans="1:3">
-      <c r="A4" s="9" t="s">
-        <v>147</v>
-      </c>
       <c r="B4" s="9" t="s">
-        <v>206</v>
+        <v>197</v>
       </c>
       <c r="C4" s="9" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3">
+      <c r="A5" s="9" t="s">
         <v>144</v>
       </c>
-    </row>
-    <row r="5" spans="1:3">
-      <c r="A5" s="9" t="s">
-        <v>148</v>
-      </c>
       <c r="B5" s="9" t="s">
-        <v>207</v>
+        <v>198</v>
       </c>
       <c r="C5" s="9" t="s">
-        <v>145</v>
+        <v>141</v>
       </c>
     </row>
   </sheetData>
@@ -1808,7 +1816,7 @@
   <cols>
     <col min="1" max="1" width="41" style="2" customWidth="1"/>
     <col min="2" max="2" width="24.6640625" style="1" customWidth="1"/>
-    <col min="3" max="3" width="9.33203125" style="2" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="13" style="2" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="36.6640625" style="2" bestFit="1" customWidth="1"/>
     <col min="5" max="16384" width="8.88671875" style="2"/>
   </cols>
@@ -1818,7 +1826,7 @@
         <v>5</v>
       </c>
       <c r="B1" s="17" t="s">
-        <v>142</v>
+        <v>138</v>
       </c>
       <c r="C1" s="17" t="s">
         <v>6</v>
@@ -1829,86 +1837,86 @@
     </row>
     <row r="2" spans="1:4">
       <c r="A2" s="5" t="s">
-        <v>208</v>
+        <v>199</v>
       </c>
       <c r="B2" s="9" t="s">
-        <v>203</v>
+        <v>194</v>
       </c>
       <c r="C2" s="5" t="s">
-        <v>8</v>
+        <v>25</v>
       </c>
       <c r="D2" s="5" t="s">
-        <v>25</v>
+        <v>213</v>
       </c>
     </row>
     <row r="3" spans="1:4">
       <c r="A3" s="5" t="s">
-        <v>209</v>
+        <v>200</v>
       </c>
       <c r="B3" s="9" t="s">
-        <v>146</v>
+        <v>142</v>
       </c>
       <c r="C3" s="5" t="s">
         <v>8</v>
       </c>
       <c r="D3" s="5" t="s">
-        <v>24</v>
+        <v>214</v>
       </c>
     </row>
     <row r="4" spans="1:4">
       <c r="A4" s="5" t="s">
-        <v>210</v>
+        <v>201</v>
       </c>
       <c r="B4" s="9" t="s">
-        <v>147</v>
+        <v>143</v>
       </c>
       <c r="C4" s="5" t="s">
         <v>8</v>
       </c>
       <c r="D4" s="5" t="s">
-        <v>26</v>
+        <v>215</v>
       </c>
     </row>
     <row r="5" spans="1:4">
       <c r="A5" s="5" t="s">
-        <v>211</v>
+        <v>202</v>
       </c>
       <c r="B5" s="9" t="s">
-        <v>147</v>
+        <v>143</v>
       </c>
       <c r="C5" s="5" t="s">
         <v>8</v>
       </c>
       <c r="D5" s="5" t="s">
-        <v>23</v>
+        <v>216</v>
       </c>
     </row>
     <row r="6" spans="1:4">
       <c r="A6" s="5" t="s">
-        <v>212</v>
+        <v>203</v>
       </c>
       <c r="B6" s="9" t="s">
-        <v>148</v>
+        <v>144</v>
       </c>
       <c r="C6" s="5" t="s">
-        <v>35</v>
+        <v>31</v>
       </c>
       <c r="D6" s="5" t="s">
-        <v>213</v>
+        <v>211</v>
       </c>
     </row>
     <row r="7" spans="1:4">
       <c r="A7" s="5" t="s">
-        <v>214</v>
+        <v>204</v>
       </c>
       <c r="B7" s="9" t="s">
-        <v>148</v>
+        <v>144</v>
       </c>
       <c r="C7" s="5" t="s">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="D7" s="5" t="s">
-        <v>215</v>
+        <v>212</v>
       </c>
     </row>
     <row r="8" spans="1:4">
@@ -28316,35 +28324,35 @@
         <v>18</v>
       </c>
       <c r="C2" s="10" t="s">
-        <v>27</v>
+        <v>23</v>
       </c>
       <c r="D2" s="12" t="s">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="E2" s="10" t="s">
         <v>20</v>
       </c>
       <c r="F2" s="10" t="s">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="G2" s="10"/>
       <c r="H2" s="10"/>
     </row>
     <row r="3" spans="1:8">
       <c r="A3" s="10" t="s">
-        <v>151</v>
+        <v>147</v>
       </c>
       <c r="B3" s="11" t="s">
-        <v>32</v>
+        <v>28</v>
       </c>
       <c r="C3" s="10" t="s">
-        <v>33</v>
+        <v>29</v>
       </c>
       <c r="D3" s="12" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="E3" s="10" t="s">
-        <v>152</v>
+        <v>148</v>
       </c>
       <c r="F3" s="10" t="s">
         <v>8</v>
@@ -28354,138 +28362,138 @@
     </row>
     <row r="4" spans="1:8">
       <c r="A4" s="10" t="s">
-        <v>31</v>
+        <v>27</v>
       </c>
       <c r="B4" s="11" t="s">
-        <v>153</v>
+        <v>149</v>
       </c>
       <c r="C4" s="10" t="s">
-        <v>37</v>
+        <v>33</v>
       </c>
       <c r="D4" s="12" t="s">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="E4" s="10" t="s">
         <v>21</v>
       </c>
       <c r="F4" s="10" t="s">
-        <v>39</v>
+        <v>35</v>
       </c>
       <c r="G4" s="10"/>
       <c r="H4" s="10"/>
     </row>
     <row r="5" spans="1:8">
       <c r="A5" s="10" t="s">
-        <v>154</v>
+        <v>150</v>
       </c>
       <c r="B5" s="11" t="s">
-        <v>41</v>
+        <v>37</v>
       </c>
       <c r="C5" s="10" t="s">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="D5" s="12" t="s">
-        <v>43</v>
+        <v>39</v>
       </c>
       <c r="E5" s="10"/>
       <c r="F5" s="10" t="s">
-        <v>155</v>
+        <v>151</v>
       </c>
       <c r="G5" s="10"/>
       <c r="H5" s="10"/>
     </row>
     <row r="6" spans="1:8">
       <c r="A6" s="10" t="s">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="B6" s="11" t="s">
-        <v>45</v>
+        <v>41</v>
       </c>
       <c r="C6" s="10" t="s">
-        <v>119</v>
+        <v>115</v>
       </c>
       <c r="D6" s="12" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="E6" s="10"/>
       <c r="F6" s="10" t="s">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="G6" s="10"/>
       <c r="H6" s="10"/>
     </row>
     <row r="7" spans="1:8">
       <c r="A7" s="10" t="s">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="B7" s="11" t="s">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="C7" s="10" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="D7" s="12" t="s">
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="E7" s="10"/>
       <c r="F7" s="10" t="s">
-        <v>35</v>
+        <v>31</v>
       </c>
       <c r="G7" s="10"/>
       <c r="H7" s="10"/>
     </row>
     <row r="8" spans="1:8">
       <c r="A8" s="10" t="s">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="B8" s="11" t="s">
-        <v>156</v>
+        <v>152</v>
       </c>
       <c r="C8" s="10" t="s">
-        <v>118</v>
+        <v>114</v>
       </c>
       <c r="D8" s="12" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="E8" s="10"/>
       <c r="F8" s="10" t="s">
-        <v>55</v>
+        <v>51</v>
       </c>
       <c r="G8" s="10"/>
       <c r="H8" s="10"/>
     </row>
     <row r="9" spans="1:8">
       <c r="A9" s="10" t="s">
-        <v>157</v>
+        <v>153</v>
       </c>
       <c r="B9" s="11" t="s">
-        <v>158</v>
+        <v>154</v>
       </c>
       <c r="C9" s="10" t="s">
-        <v>76</v>
+        <v>72</v>
       </c>
       <c r="D9" s="10" t="s">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="E9" s="10"/>
       <c r="F9" s="10" t="s">
-        <v>159</v>
+        <v>155</v>
       </c>
       <c r="G9" s="10"/>
       <c r="H9" s="10"/>
     </row>
     <row r="10" spans="1:8">
       <c r="A10" s="10" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="B10" s="11" t="s">
-        <v>56</v>
+        <v>52</v>
       </c>
       <c r="C10" s="10" t="s">
-        <v>74</v>
+        <v>70</v>
       </c>
       <c r="D10" s="10" t="s">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="E10" s="10"/>
       <c r="F10" s="10"/>
@@ -28495,13 +28503,13 @@
     <row r="11" spans="1:8">
       <c r="A11" s="10"/>
       <c r="B11" s="11" t="s">
-        <v>59</v>
+        <v>55</v>
       </c>
       <c r="C11" s="10" t="s">
-        <v>121</v>
+        <v>117</v>
       </c>
       <c r="D11" s="10" t="s">
-        <v>68</v>
+        <v>64</v>
       </c>
       <c r="E11" s="10"/>
       <c r="F11" s="10"/>
@@ -28511,10 +28519,10 @@
     <row r="12" spans="1:8">
       <c r="A12" s="13"/>
       <c r="B12" s="11" t="s">
-        <v>114</v>
+        <v>110</v>
       </c>
       <c r="C12" s="10" t="s">
-        <v>122</v>
+        <v>118</v>
       </c>
       <c r="D12" s="10" t="s">
         <v>19</v>
@@ -28527,13 +28535,13 @@
     <row r="13" spans="1:8">
       <c r="A13" s="10"/>
       <c r="B13" s="11" t="s">
-        <v>115</v>
+        <v>111</v>
       </c>
       <c r="C13" s="10" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="D13" s="10" t="s">
-        <v>64</v>
+        <v>60</v>
       </c>
       <c r="E13" s="10"/>
       <c r="F13" s="10"/>
@@ -28543,13 +28551,13 @@
     <row r="14" spans="1:8">
       <c r="A14" s="10"/>
       <c r="B14" s="11" t="s">
+        <v>112</v>
+      </c>
+      <c r="C14" s="10" t="s">
         <v>116</v>
       </c>
-      <c r="C14" s="10" t="s">
-        <v>120</v>
-      </c>
       <c r="D14" s="10" t="s">
-        <v>61</v>
+        <v>57</v>
       </c>
       <c r="E14" s="10"/>
       <c r="F14" s="10"/>
@@ -28559,13 +28567,13 @@
     <row r="15" spans="1:8">
       <c r="A15" s="10"/>
       <c r="B15" s="11" t="s">
-        <v>117</v>
+        <v>113</v>
       </c>
       <c r="C15" s="10" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="D15" s="10" t="s">
-        <v>125</v>
+        <v>121</v>
       </c>
       <c r="E15" s="10"/>
       <c r="F15" s="10"/>
@@ -28575,13 +28583,13 @@
     <row r="16" spans="1:8">
       <c r="A16" s="10"/>
       <c r="B16" s="11" t="s">
-        <v>160</v>
+        <v>156</v>
       </c>
       <c r="C16" s="10" t="s">
-        <v>57</v>
+        <v>53</v>
       </c>
       <c r="D16" s="10" t="s">
-        <v>126</v>
+        <v>122</v>
       </c>
       <c r="E16" s="10"/>
       <c r="F16" s="10"/>
@@ -28591,13 +28599,13 @@
     <row r="17" spans="1:8">
       <c r="A17" s="10"/>
       <c r="B17" s="11" t="s">
-        <v>62</v>
+        <v>58</v>
       </c>
       <c r="C17" s="10" t="s">
-        <v>60</v>
+        <v>56</v>
       </c>
       <c r="D17" s="10" t="s">
-        <v>129</v>
+        <v>125</v>
       </c>
       <c r="E17" s="10"/>
       <c r="F17" s="10"/>
@@ -28607,13 +28615,13 @@
     <row r="18" spans="1:8">
       <c r="A18" s="10"/>
       <c r="B18" s="11" t="s">
-        <v>65</v>
+        <v>61</v>
       </c>
       <c r="C18" s="10" t="s">
-        <v>63</v>
+        <v>59</v>
       </c>
       <c r="D18" s="10" t="s">
-        <v>73</v>
+        <v>69</v>
       </c>
       <c r="E18" s="10"/>
       <c r="F18" s="10"/>
@@ -28623,13 +28631,13 @@
     <row r="19" spans="1:8">
       <c r="A19" s="10"/>
       <c r="B19" s="11" t="s">
-        <v>161</v>
+        <v>157</v>
       </c>
       <c r="C19" s="10" t="s">
-        <v>66</v>
+        <v>62</v>
       </c>
       <c r="D19" s="10" t="s">
-        <v>72</v>
+        <v>68</v>
       </c>
       <c r="E19" s="10"/>
       <c r="F19" s="10"/>
@@ -28639,13 +28647,13 @@
     <row r="20" spans="1:8">
       <c r="A20" s="10"/>
       <c r="B20" s="11" t="s">
-        <v>162</v>
+        <v>158</v>
       </c>
       <c r="C20" s="10" t="s">
-        <v>67</v>
+        <v>63</v>
       </c>
       <c r="D20" s="10" t="s">
-        <v>127</v>
+        <v>123</v>
       </c>
       <c r="E20" s="10"/>
       <c r="F20" s="10"/>
@@ -28655,13 +28663,13 @@
     <row r="21" spans="1:8">
       <c r="A21" s="10"/>
       <c r="B21" s="11" t="s">
-        <v>163</v>
+        <v>159</v>
       </c>
       <c r="C21" s="10" t="s">
-        <v>69</v>
+        <v>65</v>
       </c>
       <c r="D21" s="10" t="s">
-        <v>70</v>
+        <v>66</v>
       </c>
       <c r="E21" s="10"/>
       <c r="F21" s="10"/>
@@ -28671,13 +28679,13 @@
     <row r="22" spans="1:8">
       <c r="A22" s="10"/>
       <c r="B22" s="11" t="s">
-        <v>164</v>
+        <v>160</v>
       </c>
       <c r="C22" s="10" t="s">
-        <v>71</v>
+        <v>67</v>
       </c>
       <c r="D22" s="10" t="s">
-        <v>165</v>
+        <v>161</v>
       </c>
       <c r="E22" s="10"/>
       <c r="F22" s="10"/>
@@ -28687,13 +28695,13 @@
     <row r="23" spans="1:8">
       <c r="A23" s="10"/>
       <c r="B23" s="11" t="s">
-        <v>166</v>
+        <v>162</v>
       </c>
       <c r="C23" s="10" t="s">
         <v>4</v>
       </c>
       <c r="D23" s="10" t="s">
-        <v>128</v>
+        <v>124</v>
       </c>
       <c r="E23" s="10"/>
       <c r="F23" s="10"/>
@@ -28703,13 +28711,13 @@
     <row r="24" spans="1:8">
       <c r="A24" s="10"/>
       <c r="B24" s="11" t="s">
-        <v>167</v>
+        <v>163</v>
       </c>
       <c r="C24" s="10" t="s">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="D24" s="10" t="s">
-        <v>75</v>
+        <v>71</v>
       </c>
       <c r="E24" s="10"/>
       <c r="F24" s="10"/>
@@ -28719,13 +28727,13 @@
     <row r="25" spans="1:8">
       <c r="A25" s="10"/>
       <c r="B25" s="11" t="s">
+        <v>74</v>
+      </c>
+      <c r="C25" s="10" t="s">
         <v>78</v>
       </c>
-      <c r="C25" s="10" t="s">
-        <v>82</v>
-      </c>
       <c r="D25" s="10" t="s">
-        <v>168</v>
+        <v>164</v>
       </c>
       <c r="E25" s="10"/>
       <c r="F25" s="10"/>
@@ -28735,13 +28743,13 @@
     <row r="26" spans="1:8">
       <c r="A26" s="10"/>
       <c r="B26" s="11" t="s">
+        <v>77</v>
+      </c>
+      <c r="C26" s="10" t="s">
         <v>81</v>
       </c>
-      <c r="C26" s="10" t="s">
-        <v>85</v>
-      </c>
       <c r="D26" s="10" t="s">
-        <v>77</v>
+        <v>73</v>
       </c>
       <c r="E26" s="10"/>
       <c r="F26" s="10"/>
@@ -28751,13 +28759,13 @@
     <row r="27" spans="1:8">
       <c r="A27" s="10"/>
       <c r="B27" s="11" t="s">
-        <v>84</v>
+        <v>80</v>
       </c>
       <c r="C27" s="10" t="s">
-        <v>87</v>
+        <v>83</v>
       </c>
       <c r="D27" s="10" t="s">
-        <v>80</v>
+        <v>76</v>
       </c>
       <c r="E27" s="10"/>
       <c r="F27" s="10"/>
@@ -28767,13 +28775,13 @@
     <row r="28" spans="1:8">
       <c r="A28" s="10"/>
       <c r="B28" s="11" t="s">
-        <v>169</v>
+        <v>165</v>
       </c>
       <c r="C28" s="10" t="s">
-        <v>90</v>
+        <v>86</v>
       </c>
       <c r="D28" s="10" t="s">
-        <v>83</v>
+        <v>79</v>
       </c>
       <c r="E28" s="10"/>
       <c r="F28" s="10"/>
@@ -28783,13 +28791,13 @@
     <row r="29" spans="1:8">
       <c r="A29" s="10"/>
       <c r="B29" s="10" t="s">
-        <v>89</v>
+        <v>85</v>
       </c>
       <c r="C29" s="10" t="s">
-        <v>170</v>
+        <v>166</v>
       </c>
       <c r="D29" s="10" t="s">
-        <v>86</v>
+        <v>82</v>
       </c>
       <c r="E29" s="10"/>
       <c r="F29" s="10"/>
@@ -28799,13 +28807,13 @@
     <row r="30" spans="1:8">
       <c r="A30" s="10"/>
       <c r="B30" s="10" t="s">
-        <v>92</v>
+        <v>88</v>
       </c>
       <c r="C30" s="10" t="s">
-        <v>93</v>
+        <v>89</v>
       </c>
       <c r="D30" s="10" t="s">
-        <v>88</v>
+        <v>84</v>
       </c>
       <c r="E30" s="10"/>
       <c r="F30" s="10"/>
@@ -28816,10 +28824,10 @@
       <c r="A31" s="10"/>
       <c r="B31" s="11"/>
       <c r="C31" s="10" t="s">
-        <v>95</v>
+        <v>91</v>
       </c>
       <c r="D31" s="10" t="s">
-        <v>91</v>
+        <v>87</v>
       </c>
       <c r="E31" s="10"/>
       <c r="F31" s="10"/>
@@ -28830,10 +28838,10 @@
       <c r="A32" s="10"/>
       <c r="B32" s="11"/>
       <c r="C32" s="10" t="s">
-        <v>97</v>
+        <v>93</v>
       </c>
       <c r="D32" s="10" t="s">
-        <v>94</v>
+        <v>90</v>
       </c>
       <c r="E32" s="10"/>
       <c r="F32" s="10"/>
@@ -28844,10 +28852,10 @@
       <c r="A33" s="10"/>
       <c r="B33" s="11"/>
       <c r="C33" s="10" t="s">
-        <v>99</v>
+        <v>95</v>
       </c>
       <c r="D33" s="10" t="s">
-        <v>96</v>
+        <v>92</v>
       </c>
       <c r="E33" s="10"/>
       <c r="F33" s="10"/>
@@ -28858,10 +28866,10 @@
       <c r="A34" s="10"/>
       <c r="B34" s="11"/>
       <c r="C34" s="10" t="s">
-        <v>124</v>
+        <v>120</v>
       </c>
       <c r="D34" s="10" t="s">
-        <v>130</v>
+        <v>126</v>
       </c>
       <c r="E34" s="10"/>
       <c r="F34" s="10"/>
@@ -28872,10 +28880,10 @@
       <c r="A35" s="10"/>
       <c r="B35" s="11"/>
       <c r="C35" s="10" t="s">
-        <v>123</v>
+        <v>119</v>
       </c>
       <c r="D35" s="10" t="s">
-        <v>131</v>
+        <v>127</v>
       </c>
       <c r="E35" s="10"/>
       <c r="F35" s="10"/>
@@ -28886,10 +28894,10 @@
       <c r="A36" s="10"/>
       <c r="B36" s="11"/>
       <c r="C36" s="10" t="s">
-        <v>171</v>
+        <v>167</v>
       </c>
       <c r="D36" s="10" t="s">
-        <v>132</v>
+        <v>128</v>
       </c>
       <c r="E36" s="10"/>
       <c r="F36" s="10"/>
@@ -28900,10 +28908,10 @@
       <c r="A37" s="10"/>
       <c r="B37" s="10"/>
       <c r="C37" s="10" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="D37" s="10" t="s">
-        <v>98</v>
+        <v>94</v>
       </c>
       <c r="E37" s="10"/>
       <c r="F37" s="10"/>
@@ -28915,7 +28923,7 @@
       <c r="B38" s="10"/>
       <c r="C38" s="10"/>
       <c r="D38" s="10" t="s">
-        <v>102</v>
+        <v>98</v>
       </c>
       <c r="E38" s="10"/>
       <c r="F38" s="10"/>
@@ -28927,7 +28935,7 @@
       <c r="B39" s="11"/>
       <c r="C39" s="10"/>
       <c r="D39" s="10" t="s">
-        <v>103</v>
+        <v>99</v>
       </c>
       <c r="E39" s="10"/>
       <c r="F39" s="10"/>
@@ -28939,7 +28947,7 @@
       <c r="B40" s="11"/>
       <c r="C40" s="10"/>
       <c r="D40" s="10" t="s">
-        <v>134</v>
+        <v>130</v>
       </c>
       <c r="E40" s="10"/>
       <c r="F40" s="10"/>
@@ -28948,77 +28956,77 @@
     </row>
     <row r="41" spans="1:8">
       <c r="D41" s="5" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="42" spans="1:8">
+      <c r="D42" s="5" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="43" spans="1:8">
+      <c r="D43" s="5" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="44" spans="1:8">
+      <c r="D44" s="5" t="s">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="45" spans="1:8">
+      <c r="D45" s="5" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="46" spans="1:8">
+      <c r="D46" s="5" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="47" spans="1:8">
+      <c r="D47" s="5" t="s">
         <v>104</v>
       </c>
     </row>
-    <row r="42" spans="1:8">
-      <c r="D42" s="5" t="s">
+    <row r="48" spans="1:8">
+      <c r="D48" s="5" t="s">
         <v>105</v>
       </c>
     </row>
-    <row r="43" spans="1:8">
-      <c r="D43" s="5" t="s">
-        <v>135</v>
-      </c>
-    </row>
-    <row r="44" spans="1:8">
-      <c r="D44" s="5" t="s">
-        <v>136</v>
-      </c>
-    </row>
-    <row r="45" spans="1:8">
-      <c r="D45" s="5" t="s">
+    <row r="49" spans="4:4">
+      <c r="D49" s="5" t="s">
         <v>106</v>
       </c>
     </row>
-    <row r="46" spans="1:8">
-      <c r="D46" s="5" t="s">
+    <row r="50" spans="4:4">
+      <c r="D50" s="5" t="s">
         <v>107</v>
       </c>
     </row>
-    <row r="47" spans="1:8">
-      <c r="D47" s="5" t="s">
+    <row r="51" spans="4:4">
+      <c r="D51" s="5" t="s">
         <v>108</v>
       </c>
     </row>
-    <row r="48" spans="1:8">
-      <c r="D48" s="5" t="s">
-        <v>109</v>
-      </c>
-    </row>
-    <row r="49" spans="4:4">
-      <c r="D49" s="5" t="s">
-        <v>110</v>
-      </c>
-    </row>
-    <row r="50" spans="4:4">
-      <c r="D50" s="5" t="s">
-        <v>111</v>
-      </c>
-    </row>
-    <row r="51" spans="4:4">
-      <c r="D51" s="5" t="s">
-        <v>112</v>
-      </c>
-    </row>
     <row r="52" spans="4:4">
       <c r="D52" s="5" t="s">
-        <v>100</v>
+        <v>96</v>
       </c>
     </row>
     <row r="53" spans="4:4">
       <c r="D53" s="5" t="s">
-        <v>101</v>
+        <v>97</v>
       </c>
     </row>
     <row r="54" spans="4:4">
       <c r="D54" s="5" t="s">
-        <v>133</v>
+        <v>129</v>
       </c>
     </row>
     <row r="55" spans="4:4">
       <c r="D55" s="5" t="s">
-        <v>92</v>
+        <v>88</v>
       </c>
     </row>
   </sheetData>

--- a/example-0001_dra_metadata.xlsx
+++ b/example-0001_dra_metadata.xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="23040" windowHeight="10536" tabRatio="430"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="24288" windowHeight="8952" tabRatio="430" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="Readme" sheetId="9" r:id="rId1"/>
@@ -65,7 +65,9 @@
             <family val="3"/>
             <charset val="128"/>
           </rPr>
-          <t>YYYY-MM-DD (e.g, 2024-01-01)</t>
+          <t>YYYY-MM-DD (e.g, 2024-01-01)
+For immediate release, 
+enter date of submission.</t>
         </r>
       </text>
     </comment>
@@ -565,10 +567,6 @@
     <t>AB 310 Genetic Analyzer</t>
   </si>
   <si>
-    <t>v1.0</t>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
     <t>cDNA_randomPriming</t>
   </si>
   <si>
@@ -759,10 +757,6 @@
     <phoneticPr fontId="2"/>
   </si>
   <si>
-    <t>2020-04-08 Bioinformation and DDBJ Center</t>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
     <t>This excel file is used to generate Submission, Experiment and Run XMLs for DDBJ Sequence Read Archive (DRA) submission. 
 Please see https://github.com/ddbj/submission-excel2xml for details.</t>
     <phoneticPr fontId="2"/>
@@ -906,6 +900,14 @@
   </si>
   <si>
     <t>9c349d8e07027cd6cfc49219a321a9af</t>
+  </si>
+  <si>
+    <t>2020-10-09 Bioinformation and DDBJ Center</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>v1.1</t>
+    <phoneticPr fontId="2"/>
   </si>
 </sst>
 </file>
@@ -1383,27 +1385,27 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="5" t="s">
-        <v>170</v>
+        <v>215</v>
       </c>
     </row>
     <row r="2" spans="1:1">
       <c r="A2" s="5" t="s">
-        <v>109</v>
+        <v>216</v>
       </c>
     </row>
     <row r="4" spans="1:1" ht="26.4">
       <c r="A4" s="7" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
     </row>
     <row r="6" spans="1:1">
       <c r="A6" s="16" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
     </row>
     <row r="7" spans="1:1">
       <c r="A7" s="18" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
     </row>
   </sheetData>
@@ -1429,21 +1431,21 @@
   <sheetData>
     <row r="1" spans="1:3">
       <c r="A1" s="16" t="s">
+        <v>133</v>
+      </c>
+      <c r="B1" s="16" t="s">
+        <v>132</v>
+      </c>
+      <c r="C1" s="17" t="s">
         <v>134</v>
       </c>
-      <c r="B1" s="16" t="s">
-        <v>133</v>
-      </c>
-      <c r="C1" s="17" t="s">
-        <v>135</v>
-      </c>
     </row>
     <row r="2" spans="1:3">
       <c r="A2" s="5" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="B2" s="5" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="C2" s="3">
         <v>45292</v>
@@ -1451,26 +1453,26 @@
     </row>
     <row r="4" spans="1:3">
       <c r="A4" s="16" t="s">
+        <v>135</v>
+      </c>
+      <c r="B4" s="16" t="s">
         <v>136</v>
       </c>
-      <c r="B4" s="16" t="s">
-        <v>137</v>
-      </c>
     </row>
     <row r="5" spans="1:3">
       <c r="A5" s="5" t="s">
+        <v>172</v>
+      </c>
+      <c r="B5" s="6" t="s">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3">
+      <c r="A6" s="5" t="s">
         <v>174</v>
       </c>
-      <c r="B5" s="6" t="s">
+      <c r="B6" t="s">
         <v>175</v>
-      </c>
-    </row>
-    <row r="6" spans="1:3">
-      <c r="A6" s="5" t="s">
-        <v>176</v>
-      </c>
-      <c r="B6" t="s">
-        <v>177</v>
       </c>
     </row>
     <row r="7" spans="1:3">
@@ -1506,7 +1508,7 @@
   <sheetData>
     <row r="1" spans="1:13">
       <c r="A1" s="16" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="B1" s="16" t="s">
         <v>9</v>
@@ -1547,16 +1549,16 @@
     </row>
     <row r="2" spans="1:13">
       <c r="A2" s="9" t="s">
-        <v>178</v>
+        <v>176</v>
       </c>
       <c r="B2" s="9" t="s">
-        <v>179</v>
+        <v>177</v>
       </c>
       <c r="C2" s="9" t="s">
-        <v>207</v>
+        <v>205</v>
       </c>
       <c r="D2" s="9" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="E2" s="9" t="s">
         <v>3</v>
@@ -1568,7 +1570,7 @@
         <v>23</v>
       </c>
       <c r="H2" s="9" t="s">
-        <v>181</v>
+        <v>179</v>
       </c>
       <c r="I2" s="9" t="s">
         <v>66</v>
@@ -1577,21 +1579,21 @@
         <v>20</v>
       </c>
       <c r="M2" s="9" t="s">
-        <v>205</v>
+        <v>203</v>
       </c>
     </row>
     <row r="3" spans="1:13">
       <c r="A3" s="9" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="B3" s="9" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
       <c r="C3" s="9" t="s">
-        <v>208</v>
+        <v>206</v>
       </c>
       <c r="D3" s="9" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="E3" s="9" t="s">
         <v>3</v>
@@ -1603,7 +1605,7 @@
         <v>23</v>
       </c>
       <c r="H3" s="9" t="s">
-        <v>184</v>
+        <v>182</v>
       </c>
       <c r="I3" s="9" t="s">
         <v>66</v>
@@ -1612,21 +1614,21 @@
         <v>20</v>
       </c>
       <c r="M3" s="9" t="s">
-        <v>205</v>
+        <v>203</v>
       </c>
     </row>
     <row r="4" spans="1:13">
       <c r="A4" s="9" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="B4" s="9" t="s">
-        <v>185</v>
+        <v>183</v>
       </c>
       <c r="C4" s="9" t="s">
-        <v>209</v>
+        <v>207</v>
       </c>
       <c r="D4" s="9" t="s">
-        <v>186</v>
+        <v>184</v>
       </c>
       <c r="E4" s="9" t="s">
         <v>3</v>
@@ -1638,7 +1640,7 @@
         <v>23</v>
       </c>
       <c r="H4" s="9" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
       <c r="I4" s="9" t="s">
         <v>60</v>
@@ -1647,24 +1649,24 @@
         <v>21</v>
       </c>
       <c r="K4" s="9" t="s">
+        <v>186</v>
+      </c>
+      <c r="M4" s="9" t="s">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="5" spans="1:13">
+      <c r="A5" s="9" t="s">
+        <v>140</v>
+      </c>
+      <c r="B5" s="9" t="s">
         <v>188</v>
       </c>
-      <c r="M4" s="9" t="s">
-        <v>189</v>
-      </c>
-    </row>
-    <row r="5" spans="1:13">
-      <c r="A5" s="9" t="s">
-        <v>141</v>
-      </c>
-      <c r="B5" s="9" t="s">
-        <v>190</v>
-      </c>
       <c r="C5" s="9" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="D5" s="9" t="s">
-        <v>191</v>
+        <v>189</v>
       </c>
       <c r="E5" s="9" t="s">
         <v>3</v>
@@ -1676,7 +1678,7 @@
         <v>23</v>
       </c>
       <c r="H5" s="9" t="s">
-        <v>192</v>
+        <v>190</v>
       </c>
       <c r="I5" s="9" t="s">
         <v>60</v>
@@ -1685,10 +1687,10 @@
         <v>21</v>
       </c>
       <c r="K5" s="9" t="s">
-        <v>193</v>
+        <v>191</v>
       </c>
       <c r="M5" s="9" t="s">
-        <v>206</v>
+        <v>204</v>
       </c>
     </row>
   </sheetData>
@@ -1748,7 +1750,7 @@
   <sheetData>
     <row r="1" spans="1:3">
       <c r="A1" s="16" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="B1" s="16" t="s">
         <v>9</v>
@@ -1759,46 +1761,46 @@
     </row>
     <row r="2" spans="1:3">
       <c r="A2" s="9" t="s">
+        <v>192</v>
+      </c>
+      <c r="B2" s="9" t="s">
+        <v>193</v>
+      </c>
+      <c r="C2" s="9" t="s">
+        <v>176</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3">
+      <c r="A3" s="9" t="s">
+        <v>141</v>
+      </c>
+      <c r="B3" s="9" t="s">
         <v>194</v>
       </c>
-      <c r="B2" s="9" t="s">
+      <c r="C3" s="9" t="s">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3">
+      <c r="A4" s="9" t="s">
+        <v>142</v>
+      </c>
+      <c r="B4" s="9" t="s">
         <v>195</v>
       </c>
-      <c r="C2" s="9" t="s">
-        <v>178</v>
+      <c r="C4" s="9" t="s">
+        <v>139</v>
       </c>
     </row>
-    <row r="3" spans="1:3">
-      <c r="A3" s="9" t="s">
-        <v>142</v>
+    <row r="5" spans="1:3">
+      <c r="A5" s="9" t="s">
+        <v>143</v>
       </c>
-      <c r="B3" s="9" t="s">
+      <c r="B5" s="9" t="s">
         <v>196</v>
       </c>
-      <c r="C3" s="9" t="s">
-        <v>139</v>
-      </c>
-    </row>
-    <row r="4" spans="1:3">
-      <c r="A4" s="9" t="s">
-        <v>143</v>
-      </c>
-      <c r="B4" s="9" t="s">
-        <v>197</v>
-      </c>
-      <c r="C4" s="9" t="s">
+      <c r="C5" s="9" t="s">
         <v>140</v>
-      </c>
-    </row>
-    <row r="5" spans="1:3">
-      <c r="A5" s="9" t="s">
-        <v>144</v>
-      </c>
-      <c r="B5" s="9" t="s">
-        <v>198</v>
-      </c>
-      <c r="C5" s="9" t="s">
-        <v>141</v>
       </c>
     </row>
   </sheetData>
@@ -1826,7 +1828,7 @@
         <v>5</v>
       </c>
       <c r="B1" s="17" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="C1" s="17" t="s">
         <v>6</v>
@@ -1837,86 +1839,86 @@
     </row>
     <row r="2" spans="1:4">
       <c r="A2" s="5" t="s">
-        <v>199</v>
+        <v>197</v>
       </c>
       <c r="B2" s="9" t="s">
-        <v>194</v>
+        <v>192</v>
       </c>
       <c r="C2" s="5" t="s">
         <v>25</v>
       </c>
       <c r="D2" s="5" t="s">
-        <v>213</v>
+        <v>211</v>
       </c>
     </row>
     <row r="3" spans="1:4">
       <c r="A3" s="5" t="s">
-        <v>200</v>
+        <v>198</v>
       </c>
       <c r="B3" s="9" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="C3" s="5" t="s">
         <v>8</v>
       </c>
       <c r="D3" s="5" t="s">
-        <v>214</v>
+        <v>212</v>
       </c>
     </row>
     <row r="4" spans="1:4">
       <c r="A4" s="5" t="s">
-        <v>201</v>
+        <v>199</v>
       </c>
       <c r="B4" s="9" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="C4" s="5" t="s">
         <v>8</v>
       </c>
       <c r="D4" s="5" t="s">
-        <v>215</v>
+        <v>213</v>
       </c>
     </row>
     <row r="5" spans="1:4">
       <c r="A5" s="5" t="s">
-        <v>202</v>
+        <v>200</v>
       </c>
       <c r="B5" s="9" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="C5" s="5" t="s">
         <v>8</v>
       </c>
       <c r="D5" s="5" t="s">
-        <v>216</v>
+        <v>214</v>
       </c>
     </row>
     <row r="6" spans="1:4">
       <c r="A6" s="5" t="s">
-        <v>203</v>
+        <v>201</v>
       </c>
       <c r="B6" s="9" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="C6" s="5" t="s">
         <v>31</v>
       </c>
       <c r="D6" s="5" t="s">
-        <v>211</v>
+        <v>209</v>
       </c>
     </row>
     <row r="7" spans="1:4">
       <c r="A7" s="5" t="s">
-        <v>204</v>
+        <v>202</v>
       </c>
       <c r="B7" s="9" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="C7" s="5" t="s">
         <v>26</v>
       </c>
       <c r="D7" s="5" t="s">
-        <v>212</v>
+        <v>210</v>
       </c>
     </row>
     <row r="8" spans="1:4">
@@ -28340,7 +28342,7 @@
     </row>
     <row r="3" spans="1:8">
       <c r="A3" s="10" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="B3" s="11" t="s">
         <v>28</v>
@@ -28352,7 +28354,7 @@
         <v>30</v>
       </c>
       <c r="E3" s="10" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="F3" s="10" t="s">
         <v>8</v>
@@ -28365,7 +28367,7 @@
         <v>27</v>
       </c>
       <c r="B4" s="11" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="C4" s="10" t="s">
         <v>33</v>
@@ -28384,7 +28386,7 @@
     </row>
     <row r="5" spans="1:8">
       <c r="A5" s="10" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="B5" s="11" t="s">
         <v>37</v>
@@ -28397,7 +28399,7 @@
       </c>
       <c r="E5" s="10"/>
       <c r="F5" s="10" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="G5" s="10"/>
       <c r="H5" s="10"/>
@@ -28410,7 +28412,7 @@
         <v>41</v>
       </c>
       <c r="C6" s="10" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="D6" s="12" t="s">
         <v>43</v>
@@ -28447,10 +28449,10 @@
         <v>40</v>
       </c>
       <c r="B8" s="11" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="C8" s="10" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="D8" s="12" t="s">
         <v>48</v>
@@ -28464,10 +28466,10 @@
     </row>
     <row r="9" spans="1:8">
       <c r="A9" s="10" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="B9" s="11" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="C9" s="10" t="s">
         <v>72</v>
@@ -28477,7 +28479,7 @@
       </c>
       <c r="E9" s="10"/>
       <c r="F9" s="10" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="G9" s="10"/>
       <c r="H9" s="10"/>
@@ -28506,7 +28508,7 @@
         <v>55</v>
       </c>
       <c r="C11" s="10" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="D11" s="10" t="s">
         <v>64</v>
@@ -28519,10 +28521,10 @@
     <row r="12" spans="1:8">
       <c r="A12" s="13"/>
       <c r="B12" s="11" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="C12" s="10" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="D12" s="10" t="s">
         <v>19</v>
@@ -28535,7 +28537,7 @@
     <row r="13" spans="1:8">
       <c r="A13" s="10"/>
       <c r="B13" s="11" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="C13" s="10" t="s">
         <v>47</v>
@@ -28551,10 +28553,10 @@
     <row r="14" spans="1:8">
       <c r="A14" s="10"/>
       <c r="B14" s="11" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="C14" s="10" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="D14" s="10" t="s">
         <v>57</v>
@@ -28567,13 +28569,13 @@
     <row r="15" spans="1:8">
       <c r="A15" s="10"/>
       <c r="B15" s="11" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="C15" s="10" t="s">
         <v>49</v>
       </c>
       <c r="D15" s="10" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="E15" s="10"/>
       <c r="F15" s="10"/>
@@ -28583,13 +28585,13 @@
     <row r="16" spans="1:8">
       <c r="A16" s="10"/>
       <c r="B16" s="11" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="C16" s="10" t="s">
         <v>53</v>
       </c>
       <c r="D16" s="10" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="E16" s="10"/>
       <c r="F16" s="10"/>
@@ -28605,7 +28607,7 @@
         <v>56</v>
       </c>
       <c r="D17" s="10" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="E17" s="10"/>
       <c r="F17" s="10"/>
@@ -28631,7 +28633,7 @@
     <row r="19" spans="1:8">
       <c r="A19" s="10"/>
       <c r="B19" s="11" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="C19" s="10" t="s">
         <v>62</v>
@@ -28647,13 +28649,13 @@
     <row r="20" spans="1:8">
       <c r="A20" s="10"/>
       <c r="B20" s="11" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="C20" s="10" t="s">
         <v>63</v>
       </c>
       <c r="D20" s="10" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="E20" s="10"/>
       <c r="F20" s="10"/>
@@ -28663,7 +28665,7 @@
     <row r="21" spans="1:8">
       <c r="A21" s="10"/>
       <c r="B21" s="11" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="C21" s="10" t="s">
         <v>65</v>
@@ -28679,13 +28681,13 @@
     <row r="22" spans="1:8">
       <c r="A22" s="10"/>
       <c r="B22" s="11" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="C22" s="10" t="s">
         <v>67</v>
       </c>
       <c r="D22" s="10" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="E22" s="10"/>
       <c r="F22" s="10"/>
@@ -28695,13 +28697,13 @@
     <row r="23" spans="1:8">
       <c r="A23" s="10"/>
       <c r="B23" s="11" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="C23" s="10" t="s">
         <v>4</v>
       </c>
       <c r="D23" s="10" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="E23" s="10"/>
       <c r="F23" s="10"/>
@@ -28711,7 +28713,7 @@
     <row r="24" spans="1:8">
       <c r="A24" s="10"/>
       <c r="B24" s="11" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="C24" s="10" t="s">
         <v>75</v>
@@ -28733,7 +28735,7 @@
         <v>78</v>
       </c>
       <c r="D25" s="10" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="E25" s="10"/>
       <c r="F25" s="10"/>
@@ -28775,7 +28777,7 @@
     <row r="28" spans="1:8">
       <c r="A28" s="10"/>
       <c r="B28" s="11" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="C28" s="10" t="s">
         <v>86</v>
@@ -28794,7 +28796,7 @@
         <v>85</v>
       </c>
       <c r="C29" s="10" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="D29" s="10" t="s">
         <v>82</v>
@@ -28866,10 +28868,10 @@
       <c r="A34" s="10"/>
       <c r="B34" s="11"/>
       <c r="C34" s="10" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="D34" s="10" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="E34" s="10"/>
       <c r="F34" s="10"/>
@@ -28880,10 +28882,10 @@
       <c r="A35" s="10"/>
       <c r="B35" s="11"/>
       <c r="C35" s="10" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="D35" s="10" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="E35" s="10"/>
       <c r="F35" s="10"/>
@@ -28894,10 +28896,10 @@
       <c r="A36" s="10"/>
       <c r="B36" s="11"/>
       <c r="C36" s="10" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="D36" s="10" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="E36" s="10"/>
       <c r="F36" s="10"/>
@@ -28947,7 +28949,7 @@
       <c r="B40" s="11"/>
       <c r="C40" s="10"/>
       <c r="D40" s="10" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="E40" s="10"/>
       <c r="F40" s="10"/>
@@ -28966,12 +28968,12 @@
     </row>
     <row r="43" spans="1:8">
       <c r="D43" s="5" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
     </row>
     <row r="44" spans="1:8">
       <c r="D44" s="5" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
     </row>
     <row r="45" spans="1:8">
@@ -29021,7 +29023,7 @@
     </row>
     <row r="54" spans="4:4">
       <c r="D54" s="5" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
     </row>
     <row r="55" spans="4:4">

--- a/example-0001_dra_metadata.xlsx
+++ b/example-0001_dra_metadata.xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="24288" windowHeight="8952" tabRatio="430" activeTab="1"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="23040" windowHeight="11820" tabRatio="430" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="Readme" sheetId="9" r:id="rId1"/>
@@ -68,6 +68,21 @@
           <t>YYYY-MM-DD (e.g, 2024-01-01)
 For immediate release, 
 enter date of submission.</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="D1" authorId="0" shapeId="0">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="MS P ゴシック"/>
+            <family val="3"/>
+            <charset val="128"/>
+          </rPr>
+          <t>Enter a BioProject accession (e.g., PRJDB7252) for this submission.</t>
         </r>
       </text>
     </comment>
@@ -238,7 +253,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="263" uniqueCount="217">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="268" uniqueCount="222">
   <si>
     <t>Library Source</t>
   </si>
@@ -909,6 +924,26 @@
     <t>v1.1</t>
     <phoneticPr fontId="2"/>
   </si>
+  <si>
+    <t>BioProject accession</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>PRJDB7252</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t># Enter unique aliases in the format 'Experiment-n' (e.g, Experiment-1). Do NOT use the 'DRA submission ID_Experiment_n' format (e.g., 'test-0001_Experiment_0001').</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t># Enter unique aliases in the format 'Run-n' (e.g, Run-1). Do NOT use the 'DRA submission ID_Run_n' format (e.g., 'test-0001_Run_0001').</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t># Enter unique aliases in the format 'Run-n' (e.g, Run-1). Do NOT use the 'DRA submission ID_Run_n' format (e.g., 'test-0001_Run_0001').</t>
+    <phoneticPr fontId="2"/>
+  </si>
 </sst>
 </file>
 
@@ -918,7 +953,7 @@
     <numFmt numFmtId="176" formatCode="yyyy\-mm\-dd"/>
     <numFmt numFmtId="177" formatCode="0_);\(0\)"/>
   </numFmts>
-  <fonts count="9">
+  <fonts count="10">
     <font>
       <sz val="10"/>
       <name val="Arial"/>
@@ -979,6 +1014,12 @@
       <family val="3"/>
       <charset val="128"/>
     </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FFFF0000"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
   </fonts>
   <fills count="5">
     <fill>
@@ -1029,7 +1070,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="19">
+  <cellXfs count="20">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1">
       <protection locked="0"/>
     </xf>
@@ -1086,6 +1127,9 @@
       <protection locked="0"/>
     </xf>
     <xf numFmtId="49" fontId="0" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1">
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="49" fontId="9" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1">
       <protection locked="0"/>
     </xf>
   </cellXfs>
@@ -1429,7 +1473,7 @@
     <col min="6" max="16384" width="8.88671875" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3">
+    <row r="1" spans="1:4">
       <c r="A1" s="16" t="s">
         <v>133</v>
       </c>
@@ -1439,8 +1483,11 @@
       <c r="C1" s="17" t="s">
         <v>134</v>
       </c>
-    </row>
-    <row r="2" spans="1:3">
+      <c r="D1" s="16" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4">
       <c r="A2" s="5" t="s">
         <v>170</v>
       </c>
@@ -1450,8 +1497,11 @@
       <c r="C2" s="3">
         <v>45292</v>
       </c>
-    </row>
-    <row r="4" spans="1:3">
+      <c r="D2" s="5" t="s">
+        <v>218</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4">
       <c r="A4" s="16" t="s">
         <v>135</v>
       </c>
@@ -1459,7 +1509,7 @@
         <v>136</v>
       </c>
     </row>
-    <row r="5" spans="1:3">
+    <row r="5" spans="1:4">
       <c r="A5" s="5" t="s">
         <v>172</v>
       </c>
@@ -1467,7 +1517,7 @@
         <v>173</v>
       </c>
     </row>
-    <row r="6" spans="1:3">
+    <row r="6" spans="1:4">
       <c r="A6" s="5" t="s">
         <v>174</v>
       </c>
@@ -1475,7 +1525,7 @@
         <v>175</v>
       </c>
     </row>
-    <row r="7" spans="1:3">
+    <row r="7" spans="1:4">
       <c r="B7"/>
     </row>
   </sheetData>
@@ -1487,7 +1537,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:M5"/>
+  <dimension ref="A1:M7"/>
   <sheetFormatPr defaultColWidth="8.88671875" defaultRowHeight="13.2"/>
   <cols>
     <col min="1" max="1" width="25.88671875" style="9" customWidth="1"/>
@@ -1693,6 +1743,11 @@
         <v>204</v>
       </c>
     </row>
+    <row r="7" spans="1:13">
+      <c r="A7" s="19" t="s">
+        <v>219</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="2"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -1739,7 +1794,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:C5"/>
+  <dimension ref="A1:C8"/>
   <sheetFormatPr defaultColWidth="8.88671875" defaultRowHeight="13.2"/>
   <cols>
     <col min="1" max="1" width="24.109375" style="9" customWidth="1"/>
@@ -1802,6 +1857,14 @@
       <c r="C5" s="9" t="s">
         <v>140</v>
       </c>
+    </row>
+    <row r="7" spans="1:3">
+      <c r="A7" s="19" t="s">
+        <v>221</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3">
+      <c r="A8" s="19"/>
     </row>
   </sheetData>
   <phoneticPr fontId="2"/>
@@ -1929,7 +1992,9 @@
     </row>
     <row r="9" spans="1:4">
       <c r="A9" s="5"/>
-      <c r="B9" s="9"/>
+      <c r="B9" s="19" t="s">
+        <v>220</v>
+      </c>
       <c r="C9" s="5"/>
       <c r="D9" s="5"/>
     </row>

--- a/example-0001_dra_metadata.xlsx
+++ b/example-0001_dra_metadata.xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="23040" windowHeight="11820" tabRatio="430" activeTab="1"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="23040" windowHeight="10536" tabRatio="430"/>
   </bookViews>
   <sheets>
     <sheet name="Readme" sheetId="9" r:id="rId1"/>
@@ -253,7 +253,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="268" uniqueCount="222">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="265" uniqueCount="219">
   <si>
     <t>Library Source</t>
   </si>
@@ -932,18 +932,6 @@
     <t>PRJDB7252</t>
     <phoneticPr fontId="2"/>
   </si>
-  <si>
-    <t># Enter unique aliases in the format 'Experiment-n' (e.g, Experiment-1). Do NOT use the 'DRA submission ID_Experiment_n' format (e.g., 'test-0001_Experiment_0001').</t>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
-    <t># Enter unique aliases in the format 'Run-n' (e.g, Run-1). Do NOT use the 'DRA submission ID_Run_n' format (e.g., 'test-0001_Run_0001').</t>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
-    <t># Enter unique aliases in the format 'Run-n' (e.g, Run-1). Do NOT use the 'DRA submission ID_Run_n' format (e.g., 'test-0001_Run_0001').</t>
-    <phoneticPr fontId="2"/>
-  </si>
 </sst>
 </file>
 
@@ -1744,9 +1732,7 @@
       </c>
     </row>
     <row r="7" spans="1:13">
-      <c r="A7" s="19" t="s">
-        <v>219</v>
-      </c>
+      <c r="A7" s="19"/>
     </row>
   </sheetData>
   <phoneticPr fontId="2"/>
@@ -1859,9 +1845,7 @@
       </c>
     </row>
     <row r="7" spans="1:3">
-      <c r="A7" s="19" t="s">
-        <v>221</v>
-      </c>
+      <c r="A7" s="19"/>
     </row>
     <row r="8" spans="1:3">
       <c r="A8" s="19"/>
@@ -1992,9 +1976,7 @@
     </row>
     <row r="9" spans="1:4">
       <c r="A9" s="5"/>
-      <c r="B9" s="19" t="s">
-        <v>220</v>
-      </c>
+      <c r="B9" s="19"/>
       <c r="C9" s="5"/>
       <c r="D9" s="5"/>
     </row>

--- a/example-0001_dra_metadata.xlsx
+++ b/example-0001_dra_metadata.xlsx
@@ -5,11 +5,11 @@
   <workbookPr defaultThemeVersion="153222"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\192.168.112.22\ykodama\github\submission-excel2xml\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\ddbjs4.nig.ac.jp\ykodama\github\submission-excel2xml\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="23040" windowHeight="10536" tabRatio="430"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="20124" windowHeight="8772" tabRatio="430"/>
   </bookViews>
   <sheets>
     <sheet name="Readme" sheetId="9" r:id="rId1"/>
@@ -253,7 +253,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="265" uniqueCount="219">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="276" uniqueCount="231">
   <si>
     <t>Library Source</t>
   </si>
@@ -743,16 +743,10 @@
     <t>Restriction Digest</t>
   </si>
   <si>
-    <t xml:space="preserve">Illumina MiniSeq      </t>
-  </si>
-  <si>
     <t>5-methylcytidine antibody</t>
   </si>
   <si>
     <t>MBD2 protein methyl-CpG binding domain</t>
-  </si>
-  <si>
-    <t xml:space="preserve">NextSeq 550            </t>
   </si>
   <si>
     <t>padlock probes capture method</t>
@@ -917,19 +911,61 @@
     <t>9c349d8e07027cd6cfc49219a321a9af</t>
   </si>
   <si>
-    <t>2020-10-09 Bioinformation and DDBJ Center</t>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
-    <t>v1.1</t>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
     <t>BioProject accession</t>
     <phoneticPr fontId="2"/>
   </si>
   <si>
     <t>PRJDB7252</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>Illumina MiniSeq</t>
+  </si>
+  <si>
+    <t>NextSeq 550</t>
+  </si>
+  <si>
+    <t>NextSeq 1000</t>
+  </si>
+  <si>
+    <t>NextSeq 2000</t>
+  </si>
+  <si>
+    <t>NOMe-Seq</t>
+  </si>
+  <si>
+    <t>BGISEQ-500</t>
+  </si>
+  <si>
+    <t>DNBSEQ-G400</t>
+  </si>
+  <si>
+    <t>DNBSEQ-T7</t>
+  </si>
+  <si>
+    <t>DNBSEQ-G50</t>
+  </si>
+  <si>
+    <t>MGISEQ-2000RS</t>
+  </si>
+  <si>
+    <t>Sequel II</t>
+  </si>
+  <si>
+    <t>Ion GeneStudio S5</t>
+  </si>
+  <si>
+    <t>Ion GeneStudio S5 plus</t>
+  </si>
+  <si>
+    <t>Ion GeneStudio S5 prime</t>
+  </si>
+  <si>
+    <t>2021-07-13 Bioinformation and DDBJ Center</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>v1.2</t>
     <phoneticPr fontId="2"/>
   </si>
 </sst>
@@ -1417,27 +1453,27 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="5" t="s">
-        <v>215</v>
+        <v>229</v>
       </c>
     </row>
     <row r="2" spans="1:1">
       <c r="A2" s="5" t="s">
-        <v>216</v>
+        <v>230</v>
       </c>
     </row>
     <row r="4" spans="1:1" ht="26.4">
       <c r="A4" s="7" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
     </row>
     <row r="6" spans="1:1">
       <c r="A6" s="16" t="s">
-        <v>167</v>
+        <v>165</v>
       </c>
     </row>
     <row r="7" spans="1:1">
       <c r="A7" s="18" t="s">
-        <v>168</v>
+        <v>166</v>
       </c>
     </row>
   </sheetData>
@@ -1472,21 +1508,21 @@
         <v>134</v>
       </c>
       <c r="D1" s="16" t="s">
-        <v>217</v>
+        <v>213</v>
       </c>
     </row>
     <row r="2" spans="1:4">
       <c r="A2" s="5" t="s">
-        <v>170</v>
+        <v>168</v>
       </c>
       <c r="B2" s="5" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="C2" s="3">
         <v>45292</v>
       </c>
       <c r="D2" s="5" t="s">
-        <v>218</v>
+        <v>214</v>
       </c>
     </row>
     <row r="4" spans="1:4">
@@ -1499,18 +1535,18 @@
     </row>
     <row r="5" spans="1:4">
       <c r="A5" s="5" t="s">
+        <v>170</v>
+      </c>
+      <c r="B5" s="6" t="s">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4">
+      <c r="A6" s="5" t="s">
         <v>172</v>
       </c>
-      <c r="B5" s="6" t="s">
+      <c r="B6" t="s">
         <v>173</v>
-      </c>
-    </row>
-    <row r="6" spans="1:4">
-      <c r="A6" s="5" t="s">
-        <v>174</v>
-      </c>
-      <c r="B6" t="s">
-        <v>175</v>
       </c>
     </row>
     <row r="7" spans="1:4">
@@ -1587,16 +1623,16 @@
     </row>
     <row r="2" spans="1:13">
       <c r="A2" s="9" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
       <c r="B2" s="9" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
       <c r="C2" s="9" t="s">
-        <v>205</v>
+        <v>203</v>
       </c>
       <c r="D2" s="9" t="s">
-        <v>178</v>
+        <v>176</v>
       </c>
       <c r="E2" s="9" t="s">
         <v>3</v>
@@ -1608,7 +1644,7 @@
         <v>23</v>
       </c>
       <c r="H2" s="9" t="s">
-        <v>179</v>
+        <v>177</v>
       </c>
       <c r="I2" s="9" t="s">
         <v>66</v>
@@ -1617,7 +1653,7 @@
         <v>20</v>
       </c>
       <c r="M2" s="9" t="s">
-        <v>203</v>
+        <v>201</v>
       </c>
     </row>
     <row r="3" spans="1:13">
@@ -1625,13 +1661,13 @@
         <v>138</v>
       </c>
       <c r="B3" s="9" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="C3" s="9" t="s">
-        <v>206</v>
+        <v>204</v>
       </c>
       <c r="D3" s="9" t="s">
-        <v>181</v>
+        <v>179</v>
       </c>
       <c r="E3" s="9" t="s">
         <v>3</v>
@@ -1643,7 +1679,7 @@
         <v>23</v>
       </c>
       <c r="H3" s="9" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
       <c r="I3" s="9" t="s">
         <v>66</v>
@@ -1652,7 +1688,7 @@
         <v>20</v>
       </c>
       <c r="M3" s="9" t="s">
-        <v>203</v>
+        <v>201</v>
       </c>
     </row>
     <row r="4" spans="1:13">
@@ -1660,13 +1696,13 @@
         <v>139</v>
       </c>
       <c r="B4" s="9" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="C4" s="9" t="s">
-        <v>207</v>
+        <v>205</v>
       </c>
       <c r="D4" s="9" t="s">
-        <v>184</v>
+        <v>182</v>
       </c>
       <c r="E4" s="9" t="s">
         <v>3</v>
@@ -1678,7 +1714,7 @@
         <v>23</v>
       </c>
       <c r="H4" s="9" t="s">
-        <v>185</v>
+        <v>183</v>
       </c>
       <c r="I4" s="9" t="s">
         <v>60</v>
@@ -1687,10 +1723,10 @@
         <v>21</v>
       </c>
       <c r="K4" s="9" t="s">
-        <v>186</v>
+        <v>184</v>
       </c>
       <c r="M4" s="9" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
     </row>
     <row r="5" spans="1:13">
@@ -1698,13 +1734,13 @@
         <v>140</v>
       </c>
       <c r="B5" s="9" t="s">
-        <v>188</v>
+        <v>186</v>
       </c>
       <c r="C5" s="9" t="s">
-        <v>208</v>
+        <v>206</v>
       </c>
       <c r="D5" s="9" t="s">
-        <v>189</v>
+        <v>187</v>
       </c>
       <c r="E5" s="9" t="s">
         <v>3</v>
@@ -1716,7 +1752,7 @@
         <v>23</v>
       </c>
       <c r="H5" s="9" t="s">
-        <v>190</v>
+        <v>188</v>
       </c>
       <c r="I5" s="9" t="s">
         <v>60</v>
@@ -1725,10 +1761,10 @@
         <v>21</v>
       </c>
       <c r="K5" s="9" t="s">
-        <v>191</v>
+        <v>189</v>
       </c>
       <c r="M5" s="9" t="s">
-        <v>204</v>
+        <v>202</v>
       </c>
     </row>
     <row r="7" spans="1:13">
@@ -1802,13 +1838,13 @@
     </row>
     <row r="2" spans="1:3">
       <c r="A2" s="9" t="s">
-        <v>192</v>
+        <v>190</v>
       </c>
       <c r="B2" s="9" t="s">
-        <v>193</v>
+        <v>191</v>
       </c>
       <c r="C2" s="9" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
     </row>
     <row r="3" spans="1:3">
@@ -1816,7 +1852,7 @@
         <v>141</v>
       </c>
       <c r="B3" s="9" t="s">
-        <v>194</v>
+        <v>192</v>
       </c>
       <c r="C3" s="9" t="s">
         <v>138</v>
@@ -1827,7 +1863,7 @@
         <v>142</v>
       </c>
       <c r="B4" s="9" t="s">
-        <v>195</v>
+        <v>193</v>
       </c>
       <c r="C4" s="9" t="s">
         <v>139</v>
@@ -1838,7 +1874,7 @@
         <v>143</v>
       </c>
       <c r="B5" s="9" t="s">
-        <v>196</v>
+        <v>194</v>
       </c>
       <c r="C5" s="9" t="s">
         <v>140</v>
@@ -1886,21 +1922,21 @@
     </row>
     <row r="2" spans="1:4">
       <c r="A2" s="5" t="s">
-        <v>197</v>
+        <v>195</v>
       </c>
       <c r="B2" s="9" t="s">
-        <v>192</v>
+        <v>190</v>
       </c>
       <c r="C2" s="5" t="s">
         <v>25</v>
       </c>
       <c r="D2" s="5" t="s">
-        <v>211</v>
+        <v>209</v>
       </c>
     </row>
     <row r="3" spans="1:4">
       <c r="A3" s="5" t="s">
-        <v>198</v>
+        <v>196</v>
       </c>
       <c r="B3" s="9" t="s">
         <v>141</v>
@@ -1909,12 +1945,12 @@
         <v>8</v>
       </c>
       <c r="D3" s="5" t="s">
-        <v>212</v>
+        <v>210</v>
       </c>
     </row>
     <row r="4" spans="1:4">
       <c r="A4" s="5" t="s">
-        <v>199</v>
+        <v>197</v>
       </c>
       <c r="B4" s="9" t="s">
         <v>142</v>
@@ -1923,12 +1959,12 @@
         <v>8</v>
       </c>
       <c r="D4" s="5" t="s">
-        <v>213</v>
+        <v>211</v>
       </c>
     </row>
     <row r="5" spans="1:4">
       <c r="A5" s="5" t="s">
-        <v>200</v>
+        <v>198</v>
       </c>
       <c r="B5" s="9" t="s">
         <v>142</v>
@@ -1937,12 +1973,12 @@
         <v>8</v>
       </c>
       <c r="D5" s="5" t="s">
-        <v>214</v>
+        <v>212</v>
       </c>
     </row>
     <row r="6" spans="1:4">
       <c r="A6" s="5" t="s">
-        <v>201</v>
+        <v>199</v>
       </c>
       <c r="B6" s="9" t="s">
         <v>143</v>
@@ -1951,12 +1987,12 @@
         <v>31</v>
       </c>
       <c r="D6" s="5" t="s">
-        <v>209</v>
+        <v>207</v>
       </c>
     </row>
     <row r="7" spans="1:4">
       <c r="A7" s="5" t="s">
-        <v>202</v>
+        <v>200</v>
       </c>
       <c r="B7" s="9" t="s">
         <v>143</v>
@@ -1965,7 +2001,7 @@
         <v>26</v>
       </c>
       <c r="D7" s="5" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
     </row>
     <row r="8" spans="1:4">
@@ -28329,7 +28365,7 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:H55"/>
+  <dimension ref="A1:H66"/>
   <sheetFormatPr defaultRowHeight="13.2"/>
   <cols>
     <col min="1" max="1" width="31.6640625" style="5" bestFit="1" customWidth="1"/>
@@ -28404,7 +28440,7 @@
         <v>147</v>
       </c>
       <c r="F3" s="10" t="s">
-        <v>8</v>
+        <v>35</v>
       </c>
       <c r="G3" s="10"/>
       <c r="H3" s="10"/>
@@ -28426,7 +28462,7 @@
         <v>21</v>
       </c>
       <c r="F4" s="10" t="s">
-        <v>35</v>
+        <v>150</v>
       </c>
       <c r="G4" s="10"/>
       <c r="H4" s="10"/>
@@ -28446,7 +28482,7 @@
       </c>
       <c r="E5" s="10"/>
       <c r="F5" s="10" t="s">
-        <v>150</v>
+        <v>26</v>
       </c>
       <c r="G5" s="10"/>
       <c r="H5" s="10"/>
@@ -28466,7 +28502,7 @@
       </c>
       <c r="E6" s="10"/>
       <c r="F6" s="10" t="s">
-        <v>26</v>
+        <v>31</v>
       </c>
       <c r="G6" s="10"/>
       <c r="H6" s="10"/>
@@ -28486,7 +28522,7 @@
       </c>
       <c r="E7" s="10"/>
       <c r="F7" s="10" t="s">
-        <v>31</v>
+        <v>51</v>
       </c>
       <c r="G7" s="10"/>
       <c r="H7" s="10"/>
@@ -28506,7 +28542,7 @@
       </c>
       <c r="E8" s="10"/>
       <c r="F8" s="10" t="s">
-        <v>51</v>
+        <v>154</v>
       </c>
       <c r="G8" s="10"/>
       <c r="H8" s="10"/>
@@ -28525,9 +28561,7 @@
         <v>50</v>
       </c>
       <c r="E9" s="10"/>
-      <c r="F9" s="10" t="s">
-        <v>154</v>
-      </c>
+      <c r="F9" s="10"/>
       <c r="G9" s="10"/>
       <c r="H9" s="10"/>
     </row>
@@ -28734,7 +28768,7 @@
         <v>67</v>
       </c>
       <c r="D22" s="10" t="s">
-        <v>160</v>
+        <v>215</v>
       </c>
       <c r="E22" s="10"/>
       <c r="F22" s="10"/>
@@ -28744,7 +28778,7 @@
     <row r="23" spans="1:8">
       <c r="A23" s="10"/>
       <c r="B23" s="11" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="C23" s="10" t="s">
         <v>4</v>
@@ -28760,7 +28794,7 @@
     <row r="24" spans="1:8">
       <c r="A24" s="10"/>
       <c r="B24" s="11" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="C24" s="10" t="s">
         <v>75</v>
@@ -28782,7 +28816,7 @@
         <v>78</v>
       </c>
       <c r="D25" s="10" t="s">
-        <v>163</v>
+        <v>216</v>
       </c>
       <c r="E25" s="10"/>
       <c r="F25" s="10"/>
@@ -28798,7 +28832,7 @@
         <v>81</v>
       </c>
       <c r="D26" s="10" t="s">
-        <v>73</v>
+        <v>217</v>
       </c>
       <c r="E26" s="10"/>
       <c r="F26" s="10"/>
@@ -28814,7 +28848,7 @@
         <v>83</v>
       </c>
       <c r="D27" s="10" t="s">
-        <v>76</v>
+        <v>218</v>
       </c>
       <c r="E27" s="10"/>
       <c r="F27" s="10"/>
@@ -28824,13 +28858,13 @@
     <row r="28" spans="1:8">
       <c r="A28" s="10"/>
       <c r="B28" s="11" t="s">
-        <v>164</v>
+        <v>162</v>
       </c>
       <c r="C28" s="10" t="s">
         <v>86</v>
       </c>
       <c r="D28" s="10" t="s">
-        <v>79</v>
+        <v>73</v>
       </c>
       <c r="E28" s="10"/>
       <c r="F28" s="10"/>
@@ -28843,10 +28877,10 @@
         <v>85</v>
       </c>
       <c r="C29" s="10" t="s">
-        <v>165</v>
+        <v>163</v>
       </c>
       <c r="D29" s="10" t="s">
-        <v>82</v>
+        <v>76</v>
       </c>
       <c r="E29" s="10"/>
       <c r="F29" s="10"/>
@@ -28862,7 +28896,7 @@
         <v>89</v>
       </c>
       <c r="D30" s="10" t="s">
-        <v>84</v>
+        <v>79</v>
       </c>
       <c r="E30" s="10"/>
       <c r="F30" s="10"/>
@@ -28876,7 +28910,7 @@
         <v>91</v>
       </c>
       <c r="D31" s="10" t="s">
-        <v>87</v>
+        <v>82</v>
       </c>
       <c r="E31" s="10"/>
       <c r="F31" s="10"/>
@@ -28887,10 +28921,10 @@
       <c r="A32" s="10"/>
       <c r="B32" s="11"/>
       <c r="C32" s="10" t="s">
-        <v>93</v>
+        <v>219</v>
       </c>
       <c r="D32" s="10" t="s">
-        <v>90</v>
+        <v>84</v>
       </c>
       <c r="E32" s="10"/>
       <c r="F32" s="10"/>
@@ -28901,10 +28935,10 @@
       <c r="A33" s="10"/>
       <c r="B33" s="11"/>
       <c r="C33" s="10" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="D33" s="10" t="s">
-        <v>92</v>
+        <v>87</v>
       </c>
       <c r="E33" s="10"/>
       <c r="F33" s="10"/>
@@ -28915,10 +28949,10 @@
       <c r="A34" s="10"/>
       <c r="B34" s="11"/>
       <c r="C34" s="10" t="s">
-        <v>119</v>
+        <v>95</v>
       </c>
       <c r="D34" s="10" t="s">
-        <v>125</v>
+        <v>90</v>
       </c>
       <c r="E34" s="10"/>
       <c r="F34" s="10"/>
@@ -28929,10 +28963,10 @@
       <c r="A35" s="10"/>
       <c r="B35" s="11"/>
       <c r="C35" s="10" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="D35" s="10" t="s">
-        <v>126</v>
+        <v>92</v>
       </c>
       <c r="E35" s="10"/>
       <c r="F35" s="10"/>
@@ -28943,10 +28977,10 @@
       <c r="A36" s="10"/>
       <c r="B36" s="11"/>
       <c r="C36" s="10" t="s">
-        <v>166</v>
+        <v>118</v>
       </c>
       <c r="D36" s="10" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="E36" s="10"/>
       <c r="F36" s="10"/>
@@ -28957,10 +28991,10 @@
       <c r="A37" s="10"/>
       <c r="B37" s="10"/>
       <c r="C37" s="10" t="s">
-        <v>46</v>
+        <v>164</v>
       </c>
       <c r="D37" s="10" t="s">
-        <v>94</v>
+        <v>126</v>
       </c>
       <c r="E37" s="10"/>
       <c r="F37" s="10"/>
@@ -28970,9 +29004,11 @@
     <row r="38" spans="1:8">
       <c r="A38" s="10"/>
       <c r="B38" s="10"/>
-      <c r="C38" s="10"/>
+      <c r="C38" s="10" t="s">
+        <v>46</v>
+      </c>
       <c r="D38" s="10" t="s">
-        <v>98</v>
+        <v>127</v>
       </c>
       <c r="E38" s="10"/>
       <c r="F38" s="10"/>
@@ -28984,7 +29020,7 @@
       <c r="B39" s="11"/>
       <c r="C39" s="10"/>
       <c r="D39" s="10" t="s">
-        <v>99</v>
+        <v>94</v>
       </c>
       <c r="E39" s="10"/>
       <c r="F39" s="10"/>
@@ -28996,7 +29032,7 @@
       <c r="B40" s="11"/>
       <c r="C40" s="10"/>
       <c r="D40" s="10" t="s">
-        <v>129</v>
+        <v>220</v>
       </c>
       <c r="E40" s="10"/>
       <c r="F40" s="10"/>
@@ -29005,76 +29041,131 @@
     </row>
     <row r="41" spans="1:8">
       <c r="D41" s="5" t="s">
+        <v>221</v>
+      </c>
+    </row>
+    <row r="42" spans="1:8">
+      <c r="D42" s="5" t="s">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="43" spans="1:8">
+      <c r="D43" s="5" t="s">
+        <v>223</v>
+      </c>
+    </row>
+    <row r="44" spans="1:8">
+      <c r="D44" s="5" t="s">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="45" spans="1:8">
+      <c r="D45" s="5" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="46" spans="1:8">
+      <c r="D46" s="5" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="47" spans="1:8">
+      <c r="D47" s="5" t="s">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="48" spans="1:8">
+      <c r="D48" s="5" t="s">
+        <v>225</v>
+      </c>
+    </row>
+    <row r="49" spans="4:4">
+      <c r="D49" s="5" t="s">
         <v>100</v>
       </c>
     </row>
-    <row r="42" spans="1:8">
-      <c r="D42" s="5" t="s">
+    <row r="50" spans="4:4">
+      <c r="D50" s="5" t="s">
         <v>101</v>
       </c>
     </row>
-    <row r="43" spans="1:8">
-      <c r="D43" s="5" t="s">
+    <row r="51" spans="4:4">
+      <c r="D51" s="5" t="s">
         <v>130</v>
       </c>
     </row>
-    <row r="44" spans="1:8">
-      <c r="D44" s="5" t="s">
+    <row r="52" spans="4:4">
+      <c r="D52" s="5" t="s">
         <v>131</v>
       </c>
     </row>
-    <row r="45" spans="1:8">
-      <c r="D45" s="5" t="s">
+    <row r="53" spans="4:4">
+      <c r="D53" s="5" t="s">
+        <v>226</v>
+      </c>
+    </row>
+    <row r="54" spans="4:4">
+      <c r="D54" s="5" t="s">
+        <v>227</v>
+      </c>
+    </row>
+    <row r="55" spans="4:4">
+      <c r="D55" s="5" t="s">
+        <v>228</v>
+      </c>
+    </row>
+    <row r="56" spans="4:4">
+      <c r="D56" s="5" t="s">
         <v>102</v>
       </c>
     </row>
-    <row r="46" spans="1:8">
-      <c r="D46" s="5" t="s">
+    <row r="57" spans="4:4">
+      <c r="D57" s="5" t="s">
         <v>103</v>
       </c>
     </row>
-    <row r="47" spans="1:8">
-      <c r="D47" s="5" t="s">
+    <row r="58" spans="4:4">
+      <c r="D58" s="5" t="s">
         <v>104</v>
       </c>
     </row>
-    <row r="48" spans="1:8">
-      <c r="D48" s="5" t="s">
+    <row r="59" spans="4:4">
+      <c r="D59" s="5" t="s">
         <v>105</v>
       </c>
     </row>
-    <row r="49" spans="4:4">
-      <c r="D49" s="5" t="s">
+    <row r="60" spans="4:4">
+      <c r="D60" s="5" t="s">
         <v>106</v>
       </c>
     </row>
-    <row r="50" spans="4:4">
-      <c r="D50" s="5" t="s">
+    <row r="61" spans="4:4">
+      <c r="D61" s="5" t="s">
         <v>107</v>
       </c>
     </row>
-    <row r="51" spans="4:4">
-      <c r="D51" s="5" t="s">
+    <row r="62" spans="4:4">
+      <c r="D62" s="5" t="s">
         <v>108</v>
       </c>
     </row>
-    <row r="52" spans="4:4">
-      <c r="D52" s="5" t="s">
+    <row r="63" spans="4:4">
+      <c r="D63" s="5" t="s">
         <v>96</v>
       </c>
     </row>
-    <row r="53" spans="4:4">
-      <c r="D53" s="5" t="s">
+    <row r="64" spans="4:4">
+      <c r="D64" s="5" t="s">
         <v>97</v>
       </c>
     </row>
-    <row r="54" spans="4:4">
-      <c r="D54" s="5" t="s">
+    <row r="65" spans="4:4">
+      <c r="D65" s="5" t="s">
         <v>128</v>
       </c>
     </row>
-    <row r="55" spans="4:4">
-      <c r="D55" s="5" t="s">
+    <row r="66" spans="4:4">
+      <c r="D66" s="5" t="s">
         <v>88</v>
       </c>
     </row>

--- a/example-0001_dra_metadata.xlsx
+++ b/example-0001_dra_metadata.xlsx
@@ -5,11 +5,11 @@
   <workbookPr defaultThemeVersion="153222"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\ddbjs4.nig.ac.jp\ykodama\github\submission-excel2xml\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\192.168.112.22\ykodama\github\submission-excel2xml\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="20124" windowHeight="8772" tabRatio="430"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="32424" windowHeight="8772" tabRatio="430"/>
   </bookViews>
   <sheets>
     <sheet name="Readme" sheetId="9" r:id="rId1"/>
@@ -253,7 +253,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="276" uniqueCount="231">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="276" uniqueCount="230">
   <si>
     <t>Library Source</t>
   </si>
@@ -277,9 +277,6 @@
   </si>
   <si>
     <t>MD5 Checksum</t>
-  </si>
-  <si>
-    <t>fastq</t>
   </si>
   <si>
     <t>Title</t>
@@ -1453,27 +1450,27 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="5" t="s">
+        <v>228</v>
+      </c>
+    </row>
+    <row r="2" spans="1:1">
+      <c r="A2" s="5" t="s">
         <v>229</v>
       </c>
     </row>
-    <row r="2" spans="1:1">
-      <c r="A2" s="5" t="s">
-        <v>230</v>
-      </c>
-    </row>
     <row r="4" spans="1:1" ht="26.4">
       <c r="A4" s="7" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
     </row>
     <row r="6" spans="1:1">
       <c r="A6" s="16" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
     </row>
     <row r="7" spans="1:1">
       <c r="A7" s="18" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
     </row>
   </sheetData>
@@ -1499,54 +1496,54 @@
   <sheetData>
     <row r="1" spans="1:4">
       <c r="A1" s="16" t="s">
+        <v>132</v>
+      </c>
+      <c r="B1" s="16" t="s">
+        <v>131</v>
+      </c>
+      <c r="C1" s="17" t="s">
         <v>133</v>
       </c>
-      <c r="B1" s="16" t="s">
-        <v>132</v>
-      </c>
-      <c r="C1" s="17" t="s">
-        <v>134</v>
-      </c>
       <c r="D1" s="16" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
     </row>
     <row r="2" spans="1:4">
       <c r="A2" s="5" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="B2" s="5" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="C2" s="3">
         <v>45292</v>
       </c>
       <c r="D2" s="5" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
     </row>
     <row r="4" spans="1:4">
       <c r="A4" s="16" t="s">
+        <v>134</v>
+      </c>
+      <c r="B4" s="16" t="s">
         <v>135</v>
       </c>
-      <c r="B4" s="16" t="s">
-        <v>136</v>
-      </c>
     </row>
     <row r="5" spans="1:4">
       <c r="A5" s="5" t="s">
+        <v>169</v>
+      </c>
+      <c r="B5" s="6" t="s">
         <v>170</v>
       </c>
-      <c r="B5" s="6" t="s">
+    </row>
+    <row r="6" spans="1:4">
+      <c r="A6" s="5" t="s">
         <v>171</v>
       </c>
-    </row>
-    <row r="6" spans="1:4">
-      <c r="A6" s="5" t="s">
+      <c r="B6" t="s">
         <v>172</v>
-      </c>
-      <c r="B6" t="s">
-        <v>173</v>
       </c>
     </row>
     <row r="7" spans="1:4">
@@ -1582,13 +1579,13 @@
   <sheetData>
     <row r="1" spans="1:13">
       <c r="A1" s="16" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="B1" s="16" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C1" s="16" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D1" s="16" t="s">
         <v>2</v>
@@ -1597,174 +1594,174 @@
         <v>0</v>
       </c>
       <c r="F1" s="16" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="G1" s="16" t="s">
         <v>1</v>
       </c>
       <c r="H1" s="16" t="s">
+        <v>11</v>
+      </c>
+      <c r="I1" s="16" t="s">
         <v>12</v>
       </c>
-      <c r="I1" s="16" t="s">
+      <c r="J1" s="16" t="s">
         <v>13</v>
       </c>
-      <c r="J1" s="16" t="s">
+      <c r="K1" s="18" t="s">
         <v>14</v>
       </c>
-      <c r="K1" s="18" t="s">
+      <c r="L1" s="4" t="s">
         <v>15</v>
       </c>
-      <c r="L1" s="4" t="s">
+      <c r="M1" s="16" t="s">
         <v>16</v>
       </c>
-      <c r="M1" s="16" t="s">
-        <v>17</v>
-      </c>
     </row>
     <row r="2" spans="1:13">
       <c r="A2" s="9" t="s">
+        <v>173</v>
+      </c>
+      <c r="B2" s="9" t="s">
         <v>174</v>
       </c>
-      <c r="B2" s="9" t="s">
-        <v>175</v>
-      </c>
       <c r="C2" s="9" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="D2" s="9" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="E2" s="9" t="s">
         <v>3</v>
       </c>
       <c r="F2" s="9" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="G2" s="9" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="H2" s="9" t="s">
+        <v>176</v>
+      </c>
+      <c r="I2" s="9" t="s">
+        <v>65</v>
+      </c>
+      <c r="J2" s="9" t="s">
+        <v>19</v>
+      </c>
+      <c r="M2" s="9" t="s">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="3" spans="1:13">
+      <c r="A3" s="9" t="s">
+        <v>137</v>
+      </c>
+      <c r="B3" s="9" t="s">
         <v>177</v>
       </c>
-      <c r="I2" s="9" t="s">
-        <v>66</v>
-      </c>
-      <c r="J2" s="9" t="s">
-        <v>20</v>
-      </c>
-      <c r="M2" s="9" t="s">
-        <v>201</v>
-      </c>
-    </row>
-    <row r="3" spans="1:13">
-      <c r="A3" s="9" t="s">
-        <v>138</v>
-      </c>
-      <c r="B3" s="9" t="s">
-        <v>178</v>
-      </c>
       <c r="C3" s="9" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="D3" s="9" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="E3" s="9" t="s">
         <v>3</v>
       </c>
       <c r="F3" s="9" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="G3" s="9" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="H3" s="9" t="s">
+        <v>179</v>
+      </c>
+      <c r="I3" s="9" t="s">
+        <v>65</v>
+      </c>
+      <c r="J3" s="9" t="s">
+        <v>19</v>
+      </c>
+      <c r="M3" s="9" t="s">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="4" spans="1:13">
+      <c r="A4" s="9" t="s">
+        <v>138</v>
+      </c>
+      <c r="B4" s="9" t="s">
         <v>180</v>
       </c>
-      <c r="I3" s="9" t="s">
-        <v>66</v>
-      </c>
-      <c r="J3" s="9" t="s">
-        <v>20</v>
-      </c>
-      <c r="M3" s="9" t="s">
-        <v>201</v>
-      </c>
-    </row>
-    <row r="4" spans="1:13">
-      <c r="A4" s="9" t="s">
-        <v>139</v>
-      </c>
-      <c r="B4" s="9" t="s">
-        <v>181</v>
-      </c>
       <c r="C4" s="9" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="D4" s="9" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="E4" s="9" t="s">
         <v>3</v>
       </c>
       <c r="F4" s="9" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="G4" s="9" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="H4" s="9" t="s">
+        <v>182</v>
+      </c>
+      <c r="I4" s="9" t="s">
+        <v>59</v>
+      </c>
+      <c r="J4" s="9" t="s">
+        <v>20</v>
+      </c>
+      <c r="K4" s="9" t="s">
         <v>183</v>
       </c>
-      <c r="I4" s="9" t="s">
-        <v>60</v>
-      </c>
-      <c r="J4" s="9" t="s">
-        <v>21</v>
-      </c>
-      <c r="K4" s="9" t="s">
+      <c r="M4" s="9" t="s">
         <v>184</v>
       </c>
-      <c r="M4" s="9" t="s">
+    </row>
+    <row r="5" spans="1:13">
+      <c r="A5" s="9" t="s">
+        <v>139</v>
+      </c>
+      <c r="B5" s="9" t="s">
         <v>185</v>
       </c>
-    </row>
-    <row r="5" spans="1:13">
-      <c r="A5" s="9" t="s">
-        <v>140</v>
-      </c>
-      <c r="B5" s="9" t="s">
-        <v>186</v>
-      </c>
       <c r="C5" s="9" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="D5" s="9" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="E5" s="9" t="s">
         <v>3</v>
       </c>
       <c r="F5" s="9" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="G5" s="9" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="H5" s="9" t="s">
+        <v>187</v>
+      </c>
+      <c r="I5" s="9" t="s">
+        <v>216</v>
+      </c>
+      <c r="J5" s="9" t="s">
+        <v>20</v>
+      </c>
+      <c r="K5" s="9" t="s">
         <v>188</v>
       </c>
-      <c r="I5" s="9" t="s">
-        <v>60</v>
-      </c>
-      <c r="J5" s="9" t="s">
-        <v>21</v>
-      </c>
-      <c r="K5" s="9" t="s">
-        <v>189</v>
-      </c>
       <c r="M5" s="9" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
     </row>
     <row r="7" spans="1:13">
@@ -1792,21 +1789,21 @@
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1">
           <x14:formula1>
-            <xm:f>Admin!$C$2:$C$37</xm:f>
+            <xm:f>Admin!$E$2:$E$4</xm:f>
           </x14:formula1>
-          <xm:sqref>G2:G3000</xm:sqref>
+          <xm:sqref>J2:J3000</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1">
           <x14:formula1>
-            <xm:f>Admin!$D$2:$D$55</xm:f>
+            <xm:f>Admin!$D$2:$D$66</xm:f>
           </x14:formula1>
-          <xm:sqref>I2:I3000</xm:sqref>
+          <xm:sqref>I2:I3001</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1">
           <x14:formula1>
-            <xm:f>Admin!$E$2:$E$4</xm:f>
+            <xm:f>Admin!$C$2:$C$38</xm:f>
           </x14:formula1>
-          <xm:sqref>J2:J3000</xm:sqref>
+          <xm:sqref>G2:G3001</xm:sqref>
         </x14:dataValidation>
       </x14:dataValidations>
     </ext>
@@ -1827,57 +1824,57 @@
   <sheetData>
     <row r="1" spans="1:3">
       <c r="A1" s="16" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="B1" s="16" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C1" s="16" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="2" spans="1:3">
       <c r="A2" s="9" t="s">
+        <v>189</v>
+      </c>
+      <c r="B2" s="9" t="s">
         <v>190</v>
       </c>
-      <c r="B2" s="9" t="s">
+      <c r="C2" s="9" t="s">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3">
+      <c r="A3" s="9" t="s">
+        <v>140</v>
+      </c>
+      <c r="B3" s="9" t="s">
         <v>191</v>
       </c>
-      <c r="C2" s="9" t="s">
-        <v>174</v>
+      <c r="C3" s="9" t="s">
+        <v>137</v>
       </c>
     </row>
-    <row r="3" spans="1:3">
-      <c r="A3" s="9" t="s">
+    <row r="4" spans="1:3">
+      <c r="A4" s="9" t="s">
         <v>141</v>
       </c>
-      <c r="B3" s="9" t="s">
+      <c r="B4" s="9" t="s">
         <v>192</v>
       </c>
-      <c r="C3" s="9" t="s">
+      <c r="C4" s="9" t="s">
         <v>138</v>
       </c>
     </row>
-    <row r="4" spans="1:3">
-      <c r="A4" s="9" t="s">
+    <row r="5" spans="1:3">
+      <c r="A5" s="9" t="s">
         <v>142</v>
       </c>
-      <c r="B4" s="9" t="s">
+      <c r="B5" s="9" t="s">
         <v>193</v>
       </c>
-      <c r="C4" s="9" t="s">
+      <c r="C5" s="9" t="s">
         <v>139</v>
-      </c>
-    </row>
-    <row r="5" spans="1:3">
-      <c r="A5" s="9" t="s">
-        <v>143</v>
-      </c>
-      <c r="B5" s="9" t="s">
-        <v>194</v>
-      </c>
-      <c r="C5" s="9" t="s">
-        <v>140</v>
       </c>
     </row>
     <row r="7" spans="1:3">
@@ -1911,7 +1908,7 @@
         <v>5</v>
       </c>
       <c r="B1" s="17" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="C1" s="17" t="s">
         <v>6</v>
@@ -1922,86 +1919,86 @@
     </row>
     <row r="2" spans="1:4">
       <c r="A2" s="5" t="s">
+        <v>194</v>
+      </c>
+      <c r="B2" s="9" t="s">
+        <v>189</v>
+      </c>
+      <c r="C2" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="D2" s="5" t="s">
+        <v>208</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4">
+      <c r="A3" s="5" t="s">
         <v>195</v>
       </c>
-      <c r="B2" s="9" t="s">
-        <v>190</v>
+      <c r="B3" s="9" t="s">
+        <v>140</v>
       </c>
-      <c r="C2" s="5" t="s">
+      <c r="C3" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="D3" s="5" t="s">
+        <v>209</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4">
+      <c r="A4" s="5" t="s">
+        <v>196</v>
+      </c>
+      <c r="B4" s="9" t="s">
+        <v>141</v>
+      </c>
+      <c r="C4" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="D4" s="5" t="s">
+        <v>210</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4">
+      <c r="A5" s="5" t="s">
+        <v>197</v>
+      </c>
+      <c r="B5" s="9" t="s">
+        <v>141</v>
+      </c>
+      <c r="C5" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="D5" s="5" t="s">
+        <v>211</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4">
+      <c r="A6" s="5" t="s">
+        <v>198</v>
+      </c>
+      <c r="B6" s="9" t="s">
+        <v>142</v>
+      </c>
+      <c r="C6" s="5" t="s">
+        <v>30</v>
+      </c>
+      <c r="D6" s="5" t="s">
+        <v>206</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4">
+      <c r="A7" s="5" t="s">
+        <v>199</v>
+      </c>
+      <c r="B7" s="9" t="s">
+        <v>142</v>
+      </c>
+      <c r="C7" s="5" t="s">
         <v>25</v>
       </c>
-      <c r="D2" s="5" t="s">
-        <v>209</v>
-      </c>
-    </row>
-    <row r="3" spans="1:4">
-      <c r="A3" s="5" t="s">
-        <v>196</v>
-      </c>
-      <c r="B3" s="9" t="s">
-        <v>141</v>
-      </c>
-      <c r="C3" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="D3" s="5" t="s">
-        <v>210</v>
-      </c>
-    </row>
-    <row r="4" spans="1:4">
-      <c r="A4" s="5" t="s">
-        <v>197</v>
-      </c>
-      <c r="B4" s="9" t="s">
-        <v>142</v>
-      </c>
-      <c r="C4" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="D4" s="5" t="s">
-        <v>211</v>
-      </c>
-    </row>
-    <row r="5" spans="1:4">
-      <c r="A5" s="5" t="s">
-        <v>198</v>
-      </c>
-      <c r="B5" s="9" t="s">
-        <v>142</v>
-      </c>
-      <c r="C5" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="D5" s="5" t="s">
-        <v>212</v>
-      </c>
-    </row>
-    <row r="6" spans="1:4">
-      <c r="A6" s="5" t="s">
-        <v>199</v>
-      </c>
-      <c r="B6" s="9" t="s">
-        <v>143</v>
-      </c>
-      <c r="C6" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="D6" s="5" t="s">
+      <c r="D7" s="5" t="s">
         <v>207</v>
-      </c>
-    </row>
-    <row r="7" spans="1:4">
-      <c r="A7" s="5" t="s">
-        <v>200</v>
-      </c>
-      <c r="B7" s="9" t="s">
-        <v>143</v>
-      </c>
-      <c r="C7" s="5" t="s">
-        <v>26</v>
-      </c>
-      <c r="D7" s="5" t="s">
-        <v>208</v>
       </c>
     </row>
     <row r="8" spans="1:4">
@@ -28353,9 +28350,9 @@
       <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="1">
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1">
           <x14:formula1>
-            <xm:f>Admin!$F$2:$F$9</xm:f>
+            <xm:f>Admin!$F$2:$F$8</xm:f>
           </x14:formula1>
-          <xm:sqref>C2:C3000</xm:sqref>
+          <xm:sqref>C2:C3001</xm:sqref>
         </x14:dataValidation>
       </x14:dataValidations>
     </ext>
@@ -28384,16 +28381,16 @@
         <v>0</v>
       </c>
       <c r="B1" s="14" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C1" s="14" t="s">
         <v>1</v>
       </c>
       <c r="D1" s="14" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="E1" s="14" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="F1" s="15" t="s">
         <v>6</v>
@@ -28406,159 +28403,159 @@
         <v>3</v>
       </c>
       <c r="B2" s="11" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="C2" s="10" t="s">
+        <v>22</v>
+      </c>
+      <c r="D2" s="12" t="s">
         <v>23</v>
       </c>
-      <c r="D2" s="12" t="s">
-        <v>24</v>
-      </c>
       <c r="E2" s="10" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="F2" s="10" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="G2" s="10"/>
       <c r="H2" s="10"/>
     </row>
     <row r="3" spans="1:8">
       <c r="A3" s="10" t="s">
+        <v>145</v>
+      </c>
+      <c r="B3" s="11" t="s">
+        <v>27</v>
+      </c>
+      <c r="C3" s="10" t="s">
+        <v>28</v>
+      </c>
+      <c r="D3" s="12" t="s">
+        <v>29</v>
+      </c>
+      <c r="E3" s="10" t="s">
         <v>146</v>
       </c>
-      <c r="B3" s="11" t="s">
-        <v>28</v>
-      </c>
-      <c r="C3" s="10" t="s">
-        <v>29</v>
-      </c>
-      <c r="D3" s="12" t="s">
-        <v>30</v>
-      </c>
-      <c r="E3" s="10" t="s">
-        <v>147</v>
-      </c>
       <c r="F3" s="10" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="G3" s="10"/>
       <c r="H3" s="10"/>
     </row>
     <row r="4" spans="1:8">
       <c r="A4" s="10" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="B4" s="11" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="C4" s="10" t="s">
+        <v>32</v>
+      </c>
+      <c r="D4" s="12" t="s">
         <v>33</v>
       </c>
-      <c r="D4" s="12" t="s">
-        <v>34</v>
-      </c>
       <c r="E4" s="10" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F4" s="10" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="G4" s="10"/>
       <c r="H4" s="10"/>
     </row>
     <row r="5" spans="1:8">
       <c r="A5" s="10" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="B5" s="11" t="s">
+        <v>36</v>
+      </c>
+      <c r="C5" s="10" t="s">
         <v>37</v>
       </c>
-      <c r="C5" s="10" t="s">
+      <c r="D5" s="12" t="s">
         <v>38</v>
-      </c>
-      <c r="D5" s="12" t="s">
-        <v>39</v>
       </c>
       <c r="E5" s="10"/>
       <c r="F5" s="10" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="G5" s="10"/>
       <c r="H5" s="10"/>
     </row>
     <row r="6" spans="1:8">
       <c r="A6" s="10" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="B6" s="11" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="C6" s="10" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="D6" s="12" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="E6" s="10"/>
       <c r="F6" s="10" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="G6" s="10"/>
       <c r="H6" s="10"/>
     </row>
     <row r="7" spans="1:8">
       <c r="A7" s="10" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="B7" s="11" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="C7" s="10" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="D7" s="12" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="E7" s="10"/>
       <c r="F7" s="10" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="G7" s="10"/>
       <c r="H7" s="10"/>
     </row>
     <row r="8" spans="1:8">
       <c r="A8" s="10" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B8" s="11" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="C8" s="10" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="D8" s="12" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="E8" s="10"/>
       <c r="F8" s="10" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="G8" s="10"/>
       <c r="H8" s="10"/>
     </row>
     <row r="9" spans="1:8">
       <c r="A9" s="10" t="s">
+        <v>151</v>
+      </c>
+      <c r="B9" s="11" t="s">
         <v>152</v>
       </c>
-      <c r="B9" s="11" t="s">
-        <v>153</v>
-      </c>
       <c r="C9" s="10" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="D9" s="10" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="E9" s="10"/>
       <c r="F9" s="10"/>
@@ -28567,16 +28564,16 @@
     </row>
     <row r="10" spans="1:8">
       <c r="A10" s="10" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="B10" s="11" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="C10" s="10" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="D10" s="10" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="E10" s="10"/>
       <c r="F10" s="10"/>
@@ -28586,13 +28583,13 @@
     <row r="11" spans="1:8">
       <c r="A11" s="10"/>
       <c r="B11" s="11" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="C11" s="10" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="D11" s="10" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="E11" s="10"/>
       <c r="F11" s="10"/>
@@ -28602,13 +28599,13 @@
     <row r="12" spans="1:8">
       <c r="A12" s="13"/>
       <c r="B12" s="11" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="C12" s="10" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="D12" s="10" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="E12" s="10"/>
       <c r="F12" s="10"/>
@@ -28618,13 +28615,13 @@
     <row r="13" spans="1:8">
       <c r="A13" s="10"/>
       <c r="B13" s="11" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="C13" s="10" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="D13" s="10" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="E13" s="10"/>
       <c r="F13" s="10"/>
@@ -28634,13 +28631,13 @@
     <row r="14" spans="1:8">
       <c r="A14" s="10"/>
       <c r="B14" s="11" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="C14" s="10" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="D14" s="10" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="E14" s="10"/>
       <c r="F14" s="10"/>
@@ -28650,13 +28647,13 @@
     <row r="15" spans="1:8">
       <c r="A15" s="10"/>
       <c r="B15" s="11" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="C15" s="10" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="D15" s="10" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="E15" s="10"/>
       <c r="F15" s="10"/>
@@ -28666,13 +28663,13 @@
     <row r="16" spans="1:8">
       <c r="A16" s="10"/>
       <c r="B16" s="11" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="C16" s="10" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="D16" s="10" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="E16" s="10"/>
       <c r="F16" s="10"/>
@@ -28682,13 +28679,13 @@
     <row r="17" spans="1:8">
       <c r="A17" s="10"/>
       <c r="B17" s="11" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="C17" s="10" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="D17" s="10" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="E17" s="10"/>
       <c r="F17" s="10"/>
@@ -28698,13 +28695,13 @@
     <row r="18" spans="1:8">
       <c r="A18" s="10"/>
       <c r="B18" s="11" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="C18" s="10" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="D18" s="10" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="E18" s="10"/>
       <c r="F18" s="10"/>
@@ -28714,13 +28711,13 @@
     <row r="19" spans="1:8">
       <c r="A19" s="10"/>
       <c r="B19" s="11" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="C19" s="10" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="D19" s="10" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="E19" s="10"/>
       <c r="F19" s="10"/>
@@ -28730,13 +28727,13 @@
     <row r="20" spans="1:8">
       <c r="A20" s="10"/>
       <c r="B20" s="11" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="C20" s="10" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="D20" s="10" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="E20" s="10"/>
       <c r="F20" s="10"/>
@@ -28746,13 +28743,13 @@
     <row r="21" spans="1:8">
       <c r="A21" s="10"/>
       <c r="B21" s="11" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="C21" s="10" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="D21" s="10" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="E21" s="10"/>
       <c r="F21" s="10"/>
@@ -28762,13 +28759,13 @@
     <row r="22" spans="1:8">
       <c r="A22" s="10"/>
       <c r="B22" s="11" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="C22" s="10" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="D22" s="10" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="E22" s="10"/>
       <c r="F22" s="10"/>
@@ -28778,13 +28775,13 @@
     <row r="23" spans="1:8">
       <c r="A23" s="10"/>
       <c r="B23" s="11" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="C23" s="10" t="s">
         <v>4</v>
       </c>
       <c r="D23" s="10" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="E23" s="10"/>
       <c r="F23" s="10"/>
@@ -28794,13 +28791,13 @@
     <row r="24" spans="1:8">
       <c r="A24" s="10"/>
       <c r="B24" s="11" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="C24" s="10" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="D24" s="10" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="E24" s="10"/>
       <c r="F24" s="10"/>
@@ -28810,13 +28807,13 @@
     <row r="25" spans="1:8">
       <c r="A25" s="10"/>
       <c r="B25" s="11" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="C25" s="10" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="D25" s="10" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="E25" s="10"/>
       <c r="F25" s="10"/>
@@ -28826,13 +28823,13 @@
     <row r="26" spans="1:8">
       <c r="A26" s="10"/>
       <c r="B26" s="11" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="C26" s="10" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="D26" s="10" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="E26" s="10"/>
       <c r="F26" s="10"/>
@@ -28842,13 +28839,13 @@
     <row r="27" spans="1:8">
       <c r="A27" s="10"/>
       <c r="B27" s="11" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="C27" s="10" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="D27" s="10" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="E27" s="10"/>
       <c r="F27" s="10"/>
@@ -28858,13 +28855,13 @@
     <row r="28" spans="1:8">
       <c r="A28" s="10"/>
       <c r="B28" s="11" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="C28" s="10" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="D28" s="10" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="E28" s="10"/>
       <c r="F28" s="10"/>
@@ -28874,13 +28871,13 @@
     <row r="29" spans="1:8">
       <c r="A29" s="10"/>
       <c r="B29" s="10" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="C29" s="10" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="D29" s="10" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="E29" s="10"/>
       <c r="F29" s="10"/>
@@ -28890,13 +28887,13 @@
     <row r="30" spans="1:8">
       <c r="A30" s="10"/>
       <c r="B30" s="10" t="s">
+        <v>87</v>
+      </c>
+      <c r="C30" s="10" t="s">
         <v>88</v>
       </c>
-      <c r="C30" s="10" t="s">
-        <v>89</v>
-      </c>
       <c r="D30" s="10" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="E30" s="10"/>
       <c r="F30" s="10"/>
@@ -28907,10 +28904,10 @@
       <c r="A31" s="10"/>
       <c r="B31" s="11"/>
       <c r="C31" s="10" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="D31" s="10" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="E31" s="10"/>
       <c r="F31" s="10"/>
@@ -28921,10 +28918,10 @@
       <c r="A32" s="10"/>
       <c r="B32" s="11"/>
       <c r="C32" s="10" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="D32" s="10" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="E32" s="10"/>
       <c r="F32" s="10"/>
@@ -28935,10 +28932,10 @@
       <c r="A33" s="10"/>
       <c r="B33" s="11"/>
       <c r="C33" s="10" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="D33" s="10" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="E33" s="10"/>
       <c r="F33" s="10"/>
@@ -28949,10 +28946,10 @@
       <c r="A34" s="10"/>
       <c r="B34" s="11"/>
       <c r="C34" s="10" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="D34" s="10" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="E34" s="10"/>
       <c r="F34" s="10"/>
@@ -28963,10 +28960,10 @@
       <c r="A35" s="10"/>
       <c r="B35" s="11"/>
       <c r="C35" s="10" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="D35" s="10" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="E35" s="10"/>
       <c r="F35" s="10"/>
@@ -28977,10 +28974,10 @@
       <c r="A36" s="10"/>
       <c r="B36" s="11"/>
       <c r="C36" s="10" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="D36" s="10" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="E36" s="10"/>
       <c r="F36" s="10"/>
@@ -28991,10 +28988,10 @@
       <c r="A37" s="10"/>
       <c r="B37" s="10"/>
       <c r="C37" s="10" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="D37" s="10" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="E37" s="10"/>
       <c r="F37" s="10"/>
@@ -29005,10 +29002,10 @@
       <c r="A38" s="10"/>
       <c r="B38" s="10"/>
       <c r="C38" s="10" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="D38" s="10" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="E38" s="10"/>
       <c r="F38" s="10"/>
@@ -29020,7 +29017,7 @@
       <c r="B39" s="11"/>
       <c r="C39" s="10"/>
       <c r="D39" s="10" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="E39" s="10"/>
       <c r="F39" s="10"/>
@@ -29032,7 +29029,7 @@
       <c r="B40" s="11"/>
       <c r="C40" s="10"/>
       <c r="D40" s="10" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="E40" s="10"/>
       <c r="F40" s="10"/>
@@ -29041,132 +29038,132 @@
     </row>
     <row r="41" spans="1:8">
       <c r="D41" s="5" t="s">
+        <v>220</v>
+      </c>
+    </row>
+    <row r="42" spans="1:8">
+      <c r="D42" s="5" t="s">
         <v>221</v>
       </c>
     </row>
-    <row r="42" spans="1:8">
-      <c r="D42" s="5" t="s">
+    <row r="43" spans="1:8">
+      <c r="D43" s="5" t="s">
         <v>222</v>
       </c>
     </row>
-    <row r="43" spans="1:8">
-      <c r="D43" s="5" t="s">
+    <row r="44" spans="1:8">
+      <c r="D44" s="5" t="s">
         <v>223</v>
       </c>
     </row>
-    <row r="44" spans="1:8">
-      <c r="D44" s="5" t="s">
+    <row r="45" spans="1:8">
+      <c r="D45" s="5" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="46" spans="1:8">
+      <c r="D46" s="5" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="47" spans="1:8">
+      <c r="D47" s="5" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="48" spans="1:8">
+      <c r="D48" s="5" t="s">
         <v>224</v>
       </c>
     </row>
-    <row r="45" spans="1:8">
-      <c r="D45" s="5" t="s">
-        <v>98</v>
-      </c>
-    </row>
-    <row r="46" spans="1:8">
-      <c r="D46" s="5" t="s">
+    <row r="49" spans="4:4">
+      <c r="D49" s="5" t="s">
         <v>99</v>
       </c>
     </row>
-    <row r="47" spans="1:8">
-      <c r="D47" s="5" t="s">
+    <row r="50" spans="4:4">
+      <c r="D50" s="5" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="51" spans="4:4">
+      <c r="D51" s="5" t="s">
         <v>129</v>
       </c>
     </row>
-    <row r="48" spans="1:8">
-      <c r="D48" s="5" t="s">
+    <row r="52" spans="4:4">
+      <c r="D52" s="5" t="s">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="53" spans="4:4">
+      <c r="D53" s="5" t="s">
         <v>225</v>
       </c>
     </row>
-    <row r="49" spans="4:4">
-      <c r="D49" s="5" t="s">
-        <v>100</v>
+    <row r="54" spans="4:4">
+      <c r="D54" s="5" t="s">
+        <v>226</v>
       </c>
     </row>
-    <row r="50" spans="4:4">
-      <c r="D50" s="5" t="s">
+    <row r="55" spans="4:4">
+      <c r="D55" s="5" t="s">
+        <v>227</v>
+      </c>
+    </row>
+    <row r="56" spans="4:4">
+      <c r="D56" s="5" t="s">
         <v>101</v>
       </c>
     </row>
-    <row r="51" spans="4:4">
-      <c r="D51" s="5" t="s">
-        <v>130</v>
-      </c>
-    </row>
-    <row r="52" spans="4:4">
-      <c r="D52" s="5" t="s">
-        <v>131</v>
-      </c>
-    </row>
-    <row r="53" spans="4:4">
-      <c r="D53" s="5" t="s">
-        <v>226</v>
-      </c>
-    </row>
-    <row r="54" spans="4:4">
-      <c r="D54" s="5" t="s">
-        <v>227</v>
-      </c>
-    </row>
-    <row r="55" spans="4:4">
-      <c r="D55" s="5" t="s">
-        <v>228</v>
-      </c>
-    </row>
-    <row r="56" spans="4:4">
-      <c r="D56" s="5" t="s">
+    <row r="57" spans="4:4">
+      <c r="D57" s="5" t="s">
         <v>102</v>
       </c>
     </row>
-    <row r="57" spans="4:4">
-      <c r="D57" s="5" t="s">
+    <row r="58" spans="4:4">
+      <c r="D58" s="5" t="s">
         <v>103</v>
       </c>
     </row>
-    <row r="58" spans="4:4">
-      <c r="D58" s="5" t="s">
+    <row r="59" spans="4:4">
+      <c r="D59" s="5" t="s">
         <v>104</v>
       </c>
     </row>
-    <row r="59" spans="4:4">
-      <c r="D59" s="5" t="s">
+    <row r="60" spans="4:4">
+      <c r="D60" s="5" t="s">
         <v>105</v>
       </c>
     </row>
-    <row r="60" spans="4:4">
-      <c r="D60" s="5" t="s">
+    <row r="61" spans="4:4">
+      <c r="D61" s="5" t="s">
         <v>106</v>
       </c>
     </row>
-    <row r="61" spans="4:4">
-      <c r="D61" s="5" t="s">
+    <row r="62" spans="4:4">
+      <c r="D62" s="5" t="s">
         <v>107</v>
       </c>
     </row>
-    <row r="62" spans="4:4">
-      <c r="D62" s="5" t="s">
-        <v>108</v>
-      </c>
-    </row>
     <row r="63" spans="4:4">
       <c r="D63" s="5" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="64" spans="4:4">
+      <c r="D64" s="5" t="s">
         <v>96</v>
       </c>
     </row>
-    <row r="64" spans="4:4">
-      <c r="D64" s="5" t="s">
-        <v>97</v>
-      </c>
-    </row>
     <row r="65" spans="4:4">
       <c r="D65" s="5" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
     </row>
     <row r="66" spans="4:4">
       <c r="D66" s="5" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
     </row>
   </sheetData>
